--- a/Models/КРС/results/КРС - Результаты прогнозов ХВ.xlsx
+++ b/Models/КРС/results/КРС - Результаты прогнозов ХВ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[4059.46, 3449.58, 3899.33]</t>
+          <t>[1980.04, 2804.29, 2321.35]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[4035.37, 3446.55, 3779.21]</t>
+          <t>[2412.7, 2909.66, 2608.27]</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>70.75548288798336</v>
+        <v>305.8436825456783</v>
       </c>
       <c r="G2" t="n">
-        <v>49.08141052336001</v>
+        <v>274.9849350885913</v>
       </c>
       <c r="H2" t="n">
-        <v>1.287814539072388</v>
+        <v>10.85151545883186</v>
       </c>
     </row>
     <row r="3">
@@ -514,32 +514,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[3441.1, 3889.78, 3600.63]</t>
+          <t>[3076.09, 2544.25, 3674.98]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[3446.55, 3779.21, 3691.05]</t>
+          <t>[2909.66, 2608.27, 3649.19]</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>82.52318478955463</v>
+        <v>104.0231386115827</v>
       </c>
       <c r="G3" t="n">
-        <v>68.81070334486806</v>
+        <v>85.41286662203977</v>
       </c>
       <c r="H3" t="n">
-        <v>1.844454673553976</v>
+        <v>2.960359718208698</v>
       </c>
     </row>
     <row r="4">
@@ -550,32 +550,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[3892.82, 3603.56, 3628.19]</t>
+          <t>[2473.4, 3573.49, 4340.85]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[3779.21, 3691.05, 3574.86]</t>
+          <t>[2608.27, 3649.19, 4253.58]</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>88.32641294400246</v>
+        <v>102.5296908886374</v>
       </c>
       <c r="G4" t="n">
-        <v>84.80858477631091</v>
+        <v>99.28040085381174</v>
       </c>
       <c r="H4" t="n">
-        <v>2.289402960020757</v>
+        <v>3.099015904148831</v>
       </c>
     </row>
     <row r="5">
@@ -586,32 +586,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[3558.51, 3583.37, 3877.67]</t>
+          <t>[3658.88, 4443.53, 4531.06]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[3691.05, 3574.86, 3951.41]</t>
+          <t>[3649.19, 4253.58, 3947.99]</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>87.70540018082916</v>
+        <v>354.0913445837654</v>
       </c>
       <c r="G5" t="n">
-        <v>71.59710043481225</v>
+        <v>260.9030783004325</v>
       </c>
       <c r="H5" t="n">
-        <v>1.898370230914678</v>
+        <v>6.499982041991117</v>
       </c>
     </row>
     <row r="6">
@@ -622,32 +622,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[3638.69, 3937.14, 1900.76]</t>
+          <t>[4438.89, 4526.11, 3844.21]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[3574.86, 3951.41, 2029.47]</t>
+          <t>[4253.58, 3947.99, 3588.93]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>83.35267933164593</v>
+        <v>380.234370217389</v>
       </c>
       <c r="G6" t="n">
-        <v>68.93488973954754</v>
+        <v>339.5707096243232</v>
       </c>
       <c r="H6" t="n">
-        <v>2.829501900695517</v>
+        <v>8.704339354385697</v>
       </c>
     </row>
     <row r="7">
@@ -658,32 +658,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[3908.33, 1886.7, 1915.61]</t>
+          <t>[4443.7, 3774.8, 4251.33]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[3951.41, 2029.47, 2412.7]</t>
+          <t>[3947.99, 3588.93, 4315.53]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>299.6294619947787</v>
+        <v>307.8959395232167</v>
       </c>
       <c r="G7" t="n">
-        <v>227.6445175611455</v>
+        <v>248.5924829925436</v>
       </c>
       <c r="H7" t="n">
-        <v>9.575941680603641</v>
+        <v>6.407523467315106</v>
       </c>
     </row>
     <row r="8">
@@ -694,32 +694,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[1895.66, 1924.24, 2725.91]</t>
+          <t>[3583.37, 4037.22, 3756.06]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[2029.47, 2412.7, 2909.66]</t>
+          <t>[3588.93, 4315.53, 3934.11]</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>311.0541017524873</v>
+        <v>190.7786555701887</v>
       </c>
       <c r="G8" t="n">
-        <v>268.6745536005292</v>
+        <v>153.9739846858127</v>
       </c>
       <c r="H8" t="n">
-        <v>11.05134583604498</v>
+        <v>3.709936522100679</v>
       </c>
     </row>
     <row r="9">
@@ -730,32 +730,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[1980.04, 2804.29, 2321.35]</t>
+          <t>[4038.99, 3758.6, 3768.74]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[2412.7, 2909.66, 2608.27]</t>
+          <t>[4315.53, 3934.11, 3766.97]</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>305.8436825456783</v>
+        <v>189.102531858087</v>
       </c>
       <c r="G9" t="n">
-        <v>274.9849350885913</v>
+        <v>151.2717801723223</v>
       </c>
       <c r="H9" t="n">
-        <v>10.85151545883186</v>
+        <v>3.638710622401973</v>
       </c>
     </row>
     <row r="10">
@@ -766,32 +766,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[3076.09, 2544.25, 3674.98]</t>
+          <t>[3867.45, 3876.66, 4201.83]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[2909.66, 2608.27, 3649.19]</t>
+          <t>[3934.11, 3766.97, 4346.53]</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>104.0231386115827</v>
+        <v>111.6769697229742</v>
       </c>
       <c r="G10" t="n">
-        <v>85.41286662203977</v>
+        <v>107.0193501480189</v>
       </c>
       <c r="H10" t="n">
-        <v>2.960359718208698</v>
+        <v>2.645195063785687</v>
       </c>
     </row>
     <row r="11">
@@ -802,32 +802,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[2473.4, 3573.49, 4340.85]</t>
+          <t>[3904.77, 4231.84, 2055.19]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[2608.27, 3649.19, 4253.58]</t>
+          <t>[3766.97, 4346.53, 2446.61]</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>102.5296908886374</v>
+        <v>248.564810013018</v>
       </c>
       <c r="G11" t="n">
-        <v>99.28040085381174</v>
+        <v>214.6377563560081</v>
       </c>
       <c r="H11" t="n">
-        <v>3.099015904148831</v>
+        <v>7.431776720511469</v>
       </c>
     </row>
     <row r="12">
@@ -838,32 +838,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[3745.86, 4337.55, 5609.29]</t>
+          <t>[4231.25, 6765.63, 3923.94]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[4438.18, 4677.05, 6615.11]</t>
+          <t>[4406.21, 5198.02, 3894.84]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>731.7210032188727</v>
+        <v>910.8317633536279</v>
       </c>
       <c r="G12" t="n">
-        <v>679.2146284884437</v>
+        <v>590.5553662627691</v>
       </c>
       <c r="H12" t="n">
-        <v>12.68765869530761</v>
+        <v>11.62522374448346</v>
       </c>
     </row>
     <row r="13">
@@ -874,32 +874,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[4580.29, 5925.31, 5047.99]</t>
+          <t>[6831.95, 3963.0, 4717.92]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[4677.05, 6615.11, 5874.29]</t>
+          <t>[5198.02, 3894.84, 4389.74]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>623.9562452016955</v>
+        <v>962.9969886720376</v>
       </c>
       <c r="G13" t="n">
-        <v>537.6223299730127</v>
+        <v>676.7594758337978</v>
       </c>
       <c r="H13" t="n">
-        <v>8.85432946012199</v>
+        <v>13.55332085427583</v>
       </c>
     </row>
     <row r="14">
@@ -910,32 +910,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[5958.31, 5075.99, 4995.06]</t>
+          <t>[3711.39, 4417.13, 10592.17]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[6615.11, 5874.29, 5485.3]</t>
+          <t>[3894.84, 4389.74, 10603.99]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>660.556523949238</v>
+        <v>107.3083386019484</v>
       </c>
       <c r="G14" t="n">
-        <v>648.4463718579131</v>
+        <v>74.22103116820169</v>
       </c>
       <c r="H14" t="n">
-        <v>10.81860909331889</v>
+        <v>1.815198612382573</v>
       </c>
     </row>
     <row r="15">
@@ -946,32 +946,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[5212.54, 5128.22, 8664.2]</t>
+          <t>[4467.78, 10711.76, 4398.77]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[5874.29, 5485.3, 7246.46]</t>
+          <t>[4389.74, 10603.99, 4466.24]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>926.5388623156806</v>
+        <v>86.13505268748256</v>
       </c>
       <c r="G15" t="n">
-        <v>812.192919613762</v>
+        <v>84.42827100089562</v>
       </c>
       <c r="H15" t="n">
-        <v>12.44655957020964</v>
+        <v>1.43494220071866</v>
       </c>
     </row>
     <row r="16">
@@ -982,32 +982,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[5281.98, 8923.77, 3630.33]</t>
+          <t>[10666.67, 4380.42, 4597.47]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[5485.3, 7246.46, 3784.33]</t>
+          <t>[10603.99, 4466.24, 4548.23]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>979.5263974529748</v>
+        <v>67.62298842879073</v>
       </c>
       <c r="G16" t="n">
-        <v>678.207141775511</v>
+        <v>65.91303054756706</v>
       </c>
       <c r="H16" t="n">
-        <v>10.30749438084804</v>
+        <v>1.19841124705379</v>
       </c>
     </row>
     <row r="17">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[9009.72, 3665.56, 4378.85]</t>
+          <t>[4374.37, 4591.18, 6338.82]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[7246.46, 3784.33, 4406.21]</t>
+          <t>[4466.24, 4548.23, 6574.41]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1020.447277758116</v>
+        <v>148.0842266423713</v>
       </c>
       <c r="G17" t="n">
-        <v>636.463316091525</v>
+        <v>123.470262054973</v>
       </c>
       <c r="H17" t="n">
-        <v>9.36404439718072</v>
+        <v>2.194926524699618</v>
       </c>
     </row>
     <row r="18">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[3473.42, 4145.48, 6627.8]</t>
+          <t>[4614.1, 6370.82, 5499.86]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[3784.33, 4406.21, 5198.02]</t>
+          <t>[4548.23, 6574.41, 5766.31]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>858.0824602424011</v>
+        <v>197.3031568778641</v>
       </c>
       <c r="G18" t="n">
-        <v>667.1397329616804</v>
+        <v>178.6374279772629</v>
       </c>
       <c r="H18" t="n">
-        <v>13.87975795836039</v>
+        <v>3.055259575930411</v>
       </c>
     </row>
     <row r="19">
@@ -1090,32 +1090,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[4231.25, 6765.63, 3923.94]</t>
+          <t>[6348.62, 5480.45, 5070.27]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[4406.21, 5198.02, 3894.84]</t>
+          <t>[6574.41, 5766.31, 5446.24]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>910.8317633536279</v>
+        <v>302.2423773952166</v>
       </c>
       <c r="G19" t="n">
-        <v>590.5553662627691</v>
+        <v>295.874074741461</v>
       </c>
       <c r="H19" t="n">
-        <v>11.62522374448346</v>
+        <v>5.098372346368687</v>
       </c>
     </row>
     <row r="20">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[6831.95, 3963.0, 4717.92]</t>
+          <t>[5528.44, 5114.75, 7109.31]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[5198.02, 3894.84, 4389.74]</t>
+          <t>[5766.31, 5446.24, 7109.86]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>962.9969886720376</v>
+        <v>235.561092847163</v>
       </c>
       <c r="G20" t="n">
-        <v>676.7594758337978</v>
+        <v>189.9675947700043</v>
       </c>
       <c r="H20" t="n">
-        <v>13.55332085427583</v>
+        <v>3.406460109908352</v>
       </c>
     </row>
     <row r="21">
@@ -1162,32 +1162,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[3711.39, 4417.13, 10592.17]</t>
+          <t>[5167.51, 7179.39, 3675.18]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[3894.84, 4389.74, 10603.99]</t>
+          <t>[5446.24, 7109.86, 3555.44]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>107.3083386019484</v>
+        <v>179.6874406578813</v>
       </c>
       <c r="G21" t="n">
-        <v>74.22103116820169</v>
+        <v>156.0003202111469</v>
       </c>
       <c r="H21" t="n">
-        <v>1.815198612382573</v>
+        <v>3.154522835745832</v>
       </c>
     </row>
     <row r="22">
@@ -1198,32 +1198,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[2814.88, 1972.43, 8051.05]</t>
+          <t>[5056.94, 9668.47, 8618.04]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[2868.77, 2841.48, 9201.63]</t>
+          <t>[5453.39, 11705.42, 8880.02]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>833.064853826995</v>
+        <v>1207.608206628648</v>
       </c>
       <c r="G22" t="n">
-        <v>691.1757746795421</v>
+        <v>898.4584342096468</v>
       </c>
       <c r="H22" t="n">
-        <v>14.98908819415648</v>
+        <v>9.207244636893517</v>
       </c>
     </row>
     <row r="23">
@@ -1234,32 +1234,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[1993.05, 8132.66, 2880.67]</t>
+          <t>[10065.65, 8977.98, 6874.48]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[2841.48, 9201.63, 2924.85]</t>
+          <t>[11705.42, 8880.02, 5882.78]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>788.3500464223406</v>
+        <v>1107.838771474722</v>
       </c>
       <c r="G23" t="n">
-        <v>653.8594210970344</v>
+        <v>909.8117652291018</v>
       </c>
       <c r="H23" t="n">
-        <v>14.32876839134788</v>
+        <v>10.65649931847447</v>
       </c>
     </row>
     <row r="24">
@@ -1270,32 +1270,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[9793.32, 3477.59, 5075.43]</t>
+          <t>[9764.34, 7509.5, 15221.81]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[9201.63, 2924.85, 4830.75]</t>
+          <t>[8880.02, 5882.78, 12400.36]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>488.3581135281757</v>
+        <v>1948.401187523829</v>
       </c>
       <c r="G24" t="n">
-        <v>463.0342509044505</v>
+        <v>1777.494850733529</v>
       </c>
       <c r="H24" t="n">
-        <v>10.13106176275255</v>
+        <v>20.12123434603624</v>
       </c>
     </row>
     <row r="25">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[3367.12, 4919.97, 12767.55]</t>
+          <t>[7105.29, 14421.33, 3850.34]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[2924.85, 4830.75, 13686.13]</t>
+          <t>[5882.78, 12400.36, 2992.34]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>590.8621665001405</v>
+        <v>1450.86148794021</v>
       </c>
       <c r="G25" t="n">
-        <v>483.356091118728</v>
+        <v>1367.158718935966</v>
       </c>
       <c r="H25" t="n">
-        <v>7.893221824144481</v>
+        <v>21.91734630445062</v>
       </c>
     </row>
     <row r="26">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[4569.41, 11853.65, 1852.41]</t>
+          <t>[13087.67, 3512.24, 2924.88]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[4830.75, 13686.13, 2261.91]</t>
+          <t>[12400.36, 2992.34, 2824.69]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1094.526726858501</v>
+        <v>500.909501184535</v>
       </c>
       <c r="G26" t="n">
-        <v>834.440104354283</v>
+        <v>435.7993156443475</v>
       </c>
       <c r="H26" t="n">
-        <v>12.30116047603115</v>
+        <v>8.821263125604693</v>
       </c>
     </row>
     <row r="27">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[12215.25, 1907.57, 4503.02]</t>
+          <t>[3418.8, 2846.57, 9444.26]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[13686.13, 2261.91, 5453.39]</t>
+          <t>[2992.34, 2824.69, 8660.45]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1031.543304105282</v>
+        <v>515.3320059997922</v>
       </c>
       <c r="G27" t="n">
-        <v>925.1949036330885</v>
+        <v>410.714733836044</v>
       </c>
       <c r="H27" t="n">
-        <v>14.61322031589391</v>
+        <v>8.025550869247276</v>
       </c>
     </row>
     <row r="28">
@@ -1414,32 +1414,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[2020.97, 4769.99, 9114.07]</t>
+          <t>[2642.11, 8793.75, 3003.77]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[2261.91, 5453.39, 11705.42]</t>
+          <t>[2824.69, 8660.45, 2975.6]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1553.510507460486</v>
+        <v>131.5265474497235</v>
       </c>
       <c r="G28" t="n">
-        <v>1171.898501078397</v>
+        <v>114.6826277797959</v>
       </c>
       <c r="H28" t="n">
-        <v>15.10732588913714</v>
+        <v>2.983214055136771</v>
       </c>
     </row>
     <row r="29">
@@ -1450,32 +1450,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[5056.94, 9668.47, 8618.04]</t>
+          <t>[9099.91, 3103.88, 5007.62]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[5453.39, 11705.42, 8880.02]</t>
+          <t>[8660.45, 2975.6, 4823.44]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1207.608206628648</v>
+        <v>284.9005524849375</v>
       </c>
       <c r="G29" t="n">
-        <v>898.4584342096468</v>
+        <v>250.6407325045085</v>
       </c>
       <c r="H29" t="n">
-        <v>9.207244636893517</v>
+        <v>4.401301619063556</v>
       </c>
     </row>
     <row r="30">
@@ -1486,32 +1486,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[10065.65, 8977.98, 6874.48]</t>
+          <t>[3028.5, 4885.59, 13116.46]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[11705.42, 8880.02, 5882.78]</t>
+          <t>[2975.6, 4823.44, 14601.52]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1107.838771474722</v>
+        <v>858.6953414688217</v>
       </c>
       <c r="G30" t="n">
-        <v>909.8117652291018</v>
+        <v>533.3697423843064</v>
       </c>
       <c r="H30" t="n">
-        <v>10.65649931847447</v>
+        <v>4.412256429044122</v>
       </c>
     </row>
     <row r="31">
@@ -1522,32 +1522,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[9764.34, 7509.5, 15221.81]</t>
+          <t>[4843.18, 13003.27, 2031.53]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[8880.02, 5882.78, 12400.36]</t>
+          <t>[4823.44, 14601.52, 2819.28]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1948.401187523829</v>
+        <v>1028.81013708663</v>
       </c>
       <c r="G31" t="n">
-        <v>1777.494850733529</v>
+        <v>801.9127354408796</v>
       </c>
       <c r="H31" t="n">
-        <v>20.12123434603624</v>
+        <v>13.09883040086279</v>
       </c>
     </row>
     <row r="32">
@@ -1558,32 +1558,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[1206.84, 1374.33, 1475.12]</t>
+          <t>[1577.51, 2089.06, 1840.72]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[1377.01, 1753.35, 1487.62]</t>
+          <t>[1640.07, 2317.39, 2004.6]</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>239.9813382609202</v>
+        <v>166.2349331547367</v>
       </c>
       <c r="G32" t="n">
-        <v>187.2303723222848</v>
+        <v>151.5875721652504</v>
       </c>
       <c r="H32" t="n">
-        <v>11.60505610684962</v>
+        <v>7.280740991671564</v>
       </c>
     </row>
     <row r="33">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[1474.67, 1586.24, 1096.96]</t>
+          <t>[2130.73, 1879.2, 3169.44]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[1753.35, 1487.62, 1248.3]</t>
+          <t>[2317.39, 2004.6, 3124.16]</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>191.7381782492535</v>
+        <v>132.4334380251499</v>
       </c>
       <c r="G33" t="n">
-        <v>176.2118572539273</v>
+        <v>119.1122414125259</v>
       </c>
       <c r="H33" t="n">
-        <v>11.54897524217808</v>
+        <v>5.253169142027622</v>
       </c>
     </row>
     <row r="34">
@@ -1630,32 +1630,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[1761.74, 1218.91, 1842.39]</t>
+          <t>[1964.34, 3311.09, 3501.34]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[1487.62, 1248.3, 1544.7]</t>
+          <t>[2004.6, 3124.16, 3594.82]</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>234.2541998674383</v>
+        <v>122.8857072019252</v>
       </c>
       <c r="G34" t="n">
-        <v>200.3995928835232</v>
+        <v>106.8887325713579</v>
       </c>
       <c r="H34" t="n">
-        <v>13.35091611912873</v>
+        <v>3.53065264339233</v>
       </c>
     </row>
     <row r="35">
@@ -1666,32 +1666,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[1107.55, 1675.69, 1612.49]</t>
+          <t>[3346.29, 3536.25, 1544.38]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[1248.3, 1544.7, 1559.28]</t>
+          <t>[3124.16, 3594.82, 1583.87]</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>115.1808374852401</v>
+        <v>134.5735062620823</v>
       </c>
       <c r="G35" t="n">
-        <v>108.3154756526618</v>
+        <v>106.7296353825185</v>
       </c>
       <c r="H35" t="n">
-        <v>7.722515102242449</v>
+        <v>3.744219090554398</v>
       </c>
     </row>
     <row r="36">
@@ -1702,32 +1702,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[1786.5, 1723.03, 913.52]</t>
+          <t>[3412.39, 1491.74, 1729.27]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[1544.7, 1559.28, 940.75]</t>
+          <t>[3594.82, 1583.87, 2020.86]</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>169.3351334726661</v>
+        <v>205.5811258983751</v>
       </c>
       <c r="G36" t="n">
-        <v>144.2608210865015</v>
+        <v>188.7136275182837</v>
       </c>
       <c r="H36" t="n">
-        <v>9.683324364842184</v>
+        <v>8.440048791182868</v>
       </c>
     </row>
     <row r="37">
@@ -1738,32 +1738,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[1595.67, 846.73, 1504.33]</t>
+          <t>[1530.91, 1776.28, 1648.06]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[1559.28, 940.75, 1640.07]</t>
+          <t>[1583.87, 2020.86, 1740.22]</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>97.61928670858174</v>
+        <v>153.968265745461</v>
       </c>
       <c r="G37" t="n">
-        <v>88.71527872920815</v>
+        <v>129.9014903546256</v>
       </c>
       <c r="H37" t="n">
-        <v>6.868077353189113</v>
+        <v>6.914208114007302</v>
       </c>
     </row>
     <row r="38">
@@ -1774,32 +1774,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[835.6, 1485.96, 1970.04]</t>
+          <t>[1806.67, 1675.72, 1307.02]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[940.75, 1640.07, 2317.39]</t>
+          <t>[2020.86, 1740.22, 1429.08]</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>227.6380771921771</v>
+        <v>147.1216504966624</v>
       </c>
       <c r="G38" t="n">
-        <v>202.2010568198671</v>
+        <v>133.5815912674494</v>
       </c>
       <c r="H38" t="n">
-        <v>11.85399701433965</v>
+        <v>7.615414287501321</v>
       </c>
     </row>
     <row r="39">
@@ -1810,32 +1810,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[1577.51, 2089.06, 1840.72]</t>
+          <t>[1761.9, 1382.74, 1851.83]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[1640.07, 2317.39, 2004.6]</t>
+          <t>[1740.22, 1429.08, 1686.36]</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>166.2349331547367</v>
+        <v>99.99863032328395</v>
       </c>
       <c r="G39" t="n">
-        <v>151.5875721652504</v>
+        <v>77.8306923442711</v>
       </c>
       <c r="H39" t="n">
-        <v>7.280740991671564</v>
+        <v>4.76695899108884</v>
       </c>
     </row>
     <row r="40">
@@ -1846,32 +1846,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[2130.73, 1879.2, 3169.44]</t>
+          <t>[1375.14, 1839.17, 1878.58]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[2317.39, 2004.6, 3124.16]</t>
+          <t>[1429.08, 1686.36, 1765.1]</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>132.4334380251499</v>
+        <v>114.2209821833186</v>
       </c>
       <c r="G40" t="n">
-        <v>119.1122414125259</v>
+        <v>106.745230569608</v>
       </c>
       <c r="H40" t="n">
-        <v>5.253169142027622</v>
+        <v>6.421806598234007</v>
       </c>
     </row>
     <row r="41">
@@ -1882,32 +1882,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[1964.34, 3311.09, 3501.34]</t>
+          <t>[1872.48, 1916.99, 1092.3]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[2004.6, 3124.16, 3594.82]</t>
+          <t>[1686.36, 1765.1, 1007.1]</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>122.8857072019252</v>
+        <v>147.1628896838572</v>
       </c>
       <c r="G41" t="n">
-        <v>106.8887325713579</v>
+        <v>141.0699931232577</v>
       </c>
       <c r="H41" t="n">
-        <v>3.53065264339233</v>
+        <v>9.367264061129566</v>
       </c>
     </row>
     <row r="42">
@@ -1918,32 +1918,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[1484.89, 2284.09, 2553.44]</t>
+          <t>[2834.61, 5120.54, 3304.94]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[1822.26, 2673.77, 2690.83]</t>
+          <t>[2845.28, 5000.88, 3396.22]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>307.9730210297569</v>
+        <v>87.11175886448152</v>
       </c>
       <c r="G42" t="n">
-        <v>288.1452816889601</v>
+        <v>73.8722778470207</v>
       </c>
       <c r="H42" t="n">
-        <v>12.73122863844751</v>
+        <v>1.818552606405228</v>
       </c>
     </row>
     <row r="43">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[2741.25, 3059.15, 2536.88]</t>
+          <t>[5137.66, 3315.92, 4782.0]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[2673.77, 2690.83, 2194.18]</t>
+          <t>[5000.88, 3396.22, 4578.81]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>293.0612036458042</v>
+        <v>148.8219089165876</v>
       </c>
       <c r="G43" t="n">
-        <v>259.4985876001172</v>
+        <v>140.0898900618575</v>
       </c>
       <c r="H43" t="n">
-        <v>10.61006637574032</v>
+        <v>3.179035803565291</v>
       </c>
     </row>
     <row r="44">
@@ -1990,32 +1990,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[2992.3, 2482.04, 2743.36]</t>
+          <t>[3237.35, 4669.88, 10648.39]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[2690.83, 2194.18, 3029.97]</t>
+          <t>[3396.22, 4578.81, 9958.4]</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>292.05901747248</v>
+        <v>412.1553388173192</v>
       </c>
       <c r="G44" t="n">
-        <v>291.9814446062476</v>
+        <v>313.3093917151771</v>
       </c>
       <c r="H44" t="n">
-        <v>11.2607360758023</v>
+        <v>4.531826872145468</v>
       </c>
     </row>
     <row r="45">
@@ -2026,32 +2026,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[2259.76, 2499.63, 4555.06]</t>
+          <t>[4871.97, 11104.79, 1923.09]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[2194.18, 3029.97, 5971.67]</t>
+          <t>[4578.81, 9958.4, 1594.05]</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>874.1397146497724</v>
+        <v>709.0851470755639</v>
       </c>
       <c r="G45" t="n">
-        <v>670.8470537566635</v>
+        <v>589.5258300211595</v>
       </c>
       <c r="H45" t="n">
-        <v>14.73816193664921</v>
+        <v>12.85190786095396</v>
       </c>
     </row>
     <row r="46">
@@ -2062,32 +2062,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[2435.13, 4438.63, 2997.89]</t>
+          <t>[10513.42, 1821.54, 2783.83]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[3029.97, 5971.67, 3593.38]</t>
+          <t>[9958.4, 1594.05, 2704.93]</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1009.731470310788</v>
+        <v>349.2940631671823</v>
       </c>
       <c r="G46" t="n">
-        <v>907.7933184280874</v>
+        <v>287.1353890545951</v>
       </c>
       <c r="H46" t="n">
-        <v>20.62529275049291</v>
+        <v>7.587118542414741</v>
       </c>
     </row>
     <row r="47">
@@ -2098,32 +2098,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[5511.85, 3716.12, 2899.17]</t>
+          <t>[1736.13, 2654.33, 2932.56]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[5971.67, 3593.38, 2845.28]</t>
+          <t>[1594.05, 2704.93, 2809.92]</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>276.5251802808605</v>
+        <v>112.2303012169544</v>
       </c>
       <c r="G47" t="n">
-        <v>212.1464916072647</v>
+        <v>105.1054015833805</v>
       </c>
       <c r="H47" t="n">
-        <v>4.336501225349504</v>
+        <v>5.049399648877961</v>
       </c>
     </row>
     <row r="48">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[3984.91, 3106.91, 5607.88]</t>
+          <t>[2460.05, 2719.47, 2253.48]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[3593.38, 2845.28, 5000.88]</t>
+          <t>[2704.93, 2809.92, 2204.76]</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>443.5428351714338</v>
+        <v>153.319416351367</v>
       </c>
       <c r="G48" t="n">
-        <v>420.0526909579295</v>
+        <v>128.0144451727942</v>
       </c>
       <c r="H48" t="n">
-        <v>10.74298943360267</v>
+        <v>4.827177305379418</v>
       </c>
     </row>
     <row r="49">
@@ -2170,32 +2170,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[2834.61, 5120.54, 3304.94]</t>
+          <t>[2957.47, 2449.09, 2767.99]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[2845.28, 5000.88, 3396.22]</t>
+          <t>[2809.92, 2204.76, 2856.12]</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>87.11175886448152</v>
+        <v>172.4671470789061</v>
       </c>
       <c r="G49" t="n">
-        <v>73.8722778470207</v>
+        <v>160.0028869203052</v>
       </c>
       <c r="H49" t="n">
-        <v>1.818552606405228</v>
+        <v>6.472853588418557</v>
       </c>
     </row>
     <row r="50">
@@ -2206,32 +2206,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[5137.66, 3315.92, 4782.0]</t>
+          <t>[2341.22, 2647.05, 4860.12]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[5000.88, 3396.22, 4578.81]</t>
+          <t>[2204.76, 2856.12, 6147.46]</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>148.8219089165876</v>
+        <v>757.0914898479346</v>
       </c>
       <c r="G50" t="n">
-        <v>140.0898900618575</v>
+        <v>544.2860460832281</v>
       </c>
       <c r="H50" t="n">
-        <v>3.179035803565291</v>
+        <v>11.48334263977277</v>
       </c>
     </row>
     <row r="51">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[3237.35, 4669.88, 10648.39]</t>
+          <t>[2510.56, 4611.68, 3078.78]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[3396.22, 4578.81, 9958.4]</t>
+          <t>[2856.12, 6147.46, 3723.94]</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>412.1553388173192</v>
+        <v>982.2192756498584</v>
       </c>
       <c r="G51" t="n">
-        <v>313.3093917151771</v>
+        <v>842.1664918749958</v>
       </c>
       <c r="H51" t="n">
-        <v>4.531826872145468</v>
+        <v>18.13530516136991</v>
       </c>
     </row>
     <row r="52">
@@ -2278,32 +2278,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[4.82, 3.78, 9.65]</t>
+          <t>[0.4, 1.75, 1.73]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[0.3, 4.3, 3.6]</t>
+          <t>[2.3, 12.5, 4.0]</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>4.372927803883686</v>
+        <v>6.437072129045665</v>
       </c>
       <c r="G52" t="n">
-        <v>3.699493154921523</v>
+        <v>4.974981838120303</v>
       </c>
       <c r="H52" t="n">
-        <v>562.6829487058218</v>
+        <v>75.20336162800989</v>
       </c>
     </row>
     <row r="53">
@@ -2314,32 +2314,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[3.24, 8.47, 3.11]</t>
+          <t>[1.95, 1.92, 6.09]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[4.3, 3.6, 3.6]</t>
+          <t>[12.5, 4.0, 5.9]</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.889853177161816</v>
+        <v>6.21128915045565</v>
       </c>
       <c r="G53" t="n">
-        <v>2.137891112254254</v>
+        <v>4.275598316572765</v>
       </c>
       <c r="H53" t="n">
-        <v>57.79000933193584</v>
+        <v>46.57627070452256</v>
       </c>
     </row>
     <row r="54">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[8.64, 3.19, 3.96]</t>
+          <t>[2.29, 6.98, 7.39]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[3.6, 3.6, 2.6]</t>
+          <t>[4.0, 5.9, 18.8]</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.02195279355857</v>
+        <v>6.692736530023917</v>
       </c>
       <c r="G54" t="n">
-        <v>2.269911990978061</v>
+        <v>4.735038486657938</v>
       </c>
       <c r="H54" t="n">
-        <v>67.8915827411508</v>
+        <v>40.60442975642453</v>
       </c>
     </row>
     <row r="55">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[2.95, 3.68, 2.13]</t>
+          <t>[7.25, 7.67, 4.32]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>[3.6, 2.6, 2.3]</t>
+          <t>[5.9, 18.8, 2.3]</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.7336558844933287</v>
+        <v>6.576813274910916</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6333818139435315</v>
+        <v>4.832224943458365</v>
       </c>
       <c r="H55" t="n">
-        <v>22.31590475879427</v>
+        <v>56.59123973800059</v>
       </c>
     </row>
     <row r="56">
@@ -2422,32 +2422,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[3.73, 2.17, 0.41]</t>
+          <t>[7.55, 4.24, 4.05]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[2.6, 2.3, 0.3]</t>
+          <t>[18.8, 2.3, 2.6]</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.6624182673340437</v>
+        <v>6.646595569965661</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4589904032774421</v>
+        <v>4.881341857161122</v>
       </c>
       <c r="H56" t="n">
-        <v>28.71338714835816</v>
+        <v>66.65787077935258</v>
       </c>
     </row>
     <row r="57">
@@ -2458,32 +2458,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[2.1, 0.38, 0.4]</t>
+          <t>[4.61, 4.4, 9.95]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[2.3, 0.3, 2.3]</t>
+          <t>[2.3, 2.6, 0.3]</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.106650384531883</v>
+        <v>5.819727815784616</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7281826217755087</v>
+        <v>4.584733317493458</v>
       </c>
       <c r="H57" t="n">
-        <v>39.35510086833342</v>
+        <v>1128.263542588773</v>
       </c>
     </row>
     <row r="58">
@@ -2494,32 +2494,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[0.39, 0.4, 1.77]</t>
+          <t>[4.17, 9.48, 3.94]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[0.3, 2.3, 12.5]</t>
+          <t>[2.6, 0.3, 0.0]</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6.293474712007431</v>
+        <v>5.837205779724359</v>
       </c>
       <c r="G58" t="n">
-        <v>4.239358501207691</v>
-      </c>
-      <c r="H58" t="n">
-        <v>65.74915626753607</v>
+        <v>4.894845233377701</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -2530,32 +2532,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[0.4, 1.75, 1.73]</t>
+          <t>[9.18, 3.8, 4.45]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>[2.3, 12.5, 4.0]</t>
+          <t>[0.3, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>6.437072129045665</v>
+        <v>6.139035936539593</v>
       </c>
       <c r="G59" t="n">
-        <v>4.974981838120303</v>
-      </c>
-      <c r="H59" t="n">
-        <v>75.20336162800989</v>
+        <v>5.709421045161449</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -2566,32 +2570,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[1.95, 1.92, 6.09]</t>
+          <t>[3.08, 3.64, 2.21]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[12.5, 4.0, 5.9]</t>
+          <t>[0.0, 0.0, 45.5]</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>6.21128915045565</v>
+        <v>25.14672112179712</v>
       </c>
       <c r="G60" t="n">
-        <v>4.275598316572765</v>
-      </c>
-      <c r="H60" t="n">
-        <v>46.57627070452256</v>
+        <v>16.67386283693196</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -2602,32 +2608,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[2.29, 6.98, 7.39]</t>
+          <t>[3.14, 1.87, 0.26]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[4.0, 5.9, 18.8]</t>
+          <t>[0.0, 45.5, 43.6]</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>6.692736530023917</v>
+        <v>35.55378598950672</v>
       </c>
       <c r="G61" t="n">
-        <v>4.735038486657938</v>
-      </c>
-      <c r="H61" t="n">
-        <v>40.60442975642453</v>
+        <v>30.03954589142113</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -2638,32 +2646,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[2.26, 4.37, 4.73]</t>
+          <t>[1.3, 3.26, 2.6]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>[2.2, 3.5, 3.5]</t>
+          <t>[1.7, 3.4, 2.6]</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.870060497347835</v>
+        <v>0.2464512976541712</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7200946834800046</v>
+        <v>0.181821198032838</v>
       </c>
       <c r="H62" t="n">
-        <v>20.91917359112736</v>
+        <v>9.309543823850152</v>
       </c>
     </row>
     <row r="63">
@@ -2674,32 +2682,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[4.31, 4.67, 3.51]</t>
+          <t>[3.65, 2.93, 2.29]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[3.5, 3.5, 2.7]</t>
+          <t>[3.4, 2.6, 2.0]</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.943658830920765</v>
+        <v>0.2889969636394582</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9284340192973245</v>
+        <v>0.2870410112057085</v>
       </c>
       <c r="H63" t="n">
-        <v>28.80097972791857</v>
+        <v>11.39307286510313</v>
       </c>
     </row>
     <row r="64">
@@ -2710,32 +2718,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[4.15, 3.1, 2.11]</t>
+          <t>[2.8, 2.19, 3.82]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[3.5, 2.7, 2.1]</t>
+          <t>[2.6, 2.0, 3.6]</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.4392744076998251</v>
+        <v>0.2065177158915788</v>
       </c>
       <c r="G64" t="n">
-        <v>0.351844289944689</v>
+        <v>0.206157047130792</v>
       </c>
       <c r="H64" t="n">
-        <v>11.23470074295632</v>
+        <v>7.883051004726722</v>
       </c>
     </row>
     <row r="65">
@@ -2746,32 +2754,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[2.79, 1.88, 2.8]</t>
+          <t>[2.1, 3.67, 1.44]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[2.7, 2.1, 2.7]</t>
+          <t>[2.0, 3.6, 1.7]</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.1492617819787078</v>
+        <v>0.1681127229983629</v>
       </c>
       <c r="G65" t="n">
-        <v>0.136753254615454</v>
+        <v>0.1450778554234959</v>
       </c>
       <c r="H65" t="n">
-        <v>5.845573959336234</v>
+        <v>7.504587937572555</v>
       </c>
     </row>
     <row r="66">
@@ -2782,32 +2790,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[1.84, 2.74, 2.4]</t>
+          <t>[3.59, 1.39, 2.75]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[2.1, 2.7, 1.7]</t>
+          <t>[3.6, 1.7, 2.7]</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.4325032415809552</v>
+        <v>0.1799112236389526</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3343114394300237</v>
+        <v>0.1217067907692639</v>
       </c>
       <c r="H66" t="n">
-        <v>18.39695583837932</v>
+        <v>6.717224075793419</v>
       </c>
     </row>
     <row r="67">
@@ -2818,32 +2826,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[2.95, 2.59, 1.76]</t>
+          <t>[1.39, 2.75, 3.04]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>[2.7, 1.7, 1.7]</t>
+          <t>[1.7, 2.7, 2.7]</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.5381697682014006</v>
+        <v>0.2639319925887765</v>
       </c>
       <c r="G67" t="n">
-        <v>0.402860243172849</v>
+        <v>0.2316225525697909</v>
       </c>
       <c r="H67" t="n">
-        <v>21.84990295525414</v>
+        <v>10.79540476574068</v>
       </c>
     </row>
     <row r="68">
@@ -2854,32 +2862,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[2.45, 1.65, 3.87]</t>
+          <t>[3.02, 3.32, 2.56]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[1.7, 1.7, 3.4]</t>
+          <t>[2.7, 2.7, 2.0]</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.5122998736079074</v>
+        <v>0.5170291922283969</v>
       </c>
       <c r="G68" t="n">
-        <v>0.4231804104365255</v>
+        <v>0.5000649318867776</v>
       </c>
       <c r="H68" t="n">
-        <v>20.32566492208529</v>
+        <v>20.95941510069665</v>
       </c>
     </row>
     <row r="69">
@@ -2890,32 +2898,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[1.3, 3.26, 2.6]</t>
+          <t>[3.12, 2.4, 1.68]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>[1.7, 3.4, 2.6]</t>
+          <t>[2.7, 2.0, 2.1]</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.2464512976541712</v>
+        <v>0.4152399797928206</v>
       </c>
       <c r="G69" t="n">
-        <v>0.181821198032838</v>
+        <v>0.4151455937526715</v>
       </c>
       <c r="H69" t="n">
-        <v>9.309543823850152</v>
+        <v>18.59591152467821</v>
       </c>
     </row>
     <row r="70">
@@ -2926,32 +2934,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[3.65, 2.93, 2.29]</t>
+          <t>[2.2, 1.52, 2.18]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[3.4, 2.6, 2.0]</t>
+          <t>[2.0, 2.1, 2.6]</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.2889969636394582</v>
+        <v>0.4297631981124362</v>
       </c>
       <c r="G70" t="n">
-        <v>0.2870410112057085</v>
+        <v>0.4011328486812731</v>
       </c>
       <c r="H70" t="n">
-        <v>11.39307286510313</v>
+        <v>17.96604603352019</v>
       </c>
     </row>
     <row r="71">
@@ -2962,32 +2970,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[2.8, 2.19, 3.82]</t>
+          <t>[1.43, 2.06, 1.62]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[2.6, 2.0, 3.6]</t>
+          <t>[2.1, 2.6, 1.7]</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.2065177158915788</v>
+        <v>0.498562196525375</v>
       </c>
       <c r="G71" t="n">
-        <v>0.206157047130792</v>
+        <v>0.4296742252434619</v>
       </c>
       <c r="H71" t="n">
-        <v>7.883051004726722</v>
+        <v>19.10949887566284</v>
       </c>
     </row>
     <row r="72">
@@ -2998,32 +3006,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[628.29, 567.11, 473.95]</t>
+          <t>[290.75, 236.78, 307.9]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>[767.55, 593.84, 518.43]</t>
+          <t>[352.82, 350.02, 466.45]</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>85.80250246611959</v>
+        <v>118.0605770830391</v>
       </c>
       <c r="G72" t="n">
-        <v>70.15646626151373</v>
+        <v>111.2869880553217</v>
       </c>
       <c r="H72" t="n">
-        <v>10.40805997028222</v>
+        <v>27.97863213645904</v>
       </c>
     </row>
     <row r="73">
@@ -3034,32 +3042,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[646.08, 538.74, 1040.66]</t>
+          <t>[270.33, 350.89, 243.16]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[593.84, 518.43, 523.12]</t>
+          <t>[350.02, 466.45, 494.05]</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>300.5499561932866</v>
+        <v>165.9810511203805</v>
       </c>
       <c r="G73" t="n">
-        <v>196.6953706541598</v>
+        <v>148.7124550948256</v>
       </c>
       <c r="H73" t="n">
-        <v>37.21575392356406</v>
+        <v>32.7745396105605</v>
       </c>
     </row>
     <row r="74">
@@ -3070,32 +3078,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[510.71, 987.16, 1005.11]</t>
+          <t>[419.67, 290.24, 626.9]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>[518.43, 523.12, 420.32]</t>
+          <t>[466.45, 494.05, 744.54]</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>431.0329216722479</v>
+        <v>138.5248046280923</v>
       </c>
       <c r="G74" t="n">
-        <v>352.1822147027944</v>
+        <v>122.7445910415628</v>
       </c>
       <c r="H74" t="n">
-        <v>76.44143201922006</v>
+        <v>22.36106482667982</v>
       </c>
     </row>
     <row r="75">
@@ -3106,32 +3114,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[996.83, 1014.7, 1338.83]</t>
+          <t>[312.53, 674.31, 550.97]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>[523.12, 420.32, 545.23]</t>
+          <t>[494.05, 744.54, 663.61]</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>634.4274594143394</v>
+        <v>129.8332010783744</v>
       </c>
       <c r="G75" t="n">
-        <v>620.5652159519276</v>
+        <v>121.4634773692033</v>
       </c>
       <c r="H75" t="n">
-        <v>125.840178994192</v>
+        <v>21.04930151490477</v>
       </c>
     </row>
     <row r="76">
@@ -3142,32 +3150,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[673.43, 895.15, 455.0]</t>
+          <t>[931.87, 758.39, 666.97]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>[420.32, 545.23, 375.66]</t>
+          <t>[744.54, 663.61, 623.57]</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>253.5103003451893</v>
+        <v>123.7721557395449</v>
       </c>
       <c r="G76" t="n">
-        <v>227.4568795046072</v>
+        <v>108.5029925881645</v>
       </c>
       <c r="H76" t="n">
-        <v>48.50574005874589</v>
+        <v>15.4676013953455</v>
       </c>
     </row>
     <row r="77">
@@ -3178,32 +3186,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[645.99, 329.74, 275.74]</t>
+          <t>[647.85, 570.88, 481.42]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>[545.23, 375.66, 352.82]</t>
+          <t>[663.61, 623.57, 400.39]</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>77.89419246693789</v>
+        <v>56.53744782166245</v>
       </c>
       <c r="G77" t="n">
-        <v>74.58643316278842</v>
+        <v>49.8237697808388</v>
       </c>
       <c r="H77" t="n">
-        <v>17.51697703092978</v>
+        <v>10.35355455059209</v>
       </c>
     </row>
     <row r="78">
@@ -3214,32 +3222,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[292.25, 244.81, 199.8]</t>
+          <t>[580.44, 489.38, 851.14]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>[375.66, 352.82, 350.02]</t>
+          <t>[623.57, 400.39, 403.4]</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>117.1736248631201</v>
+        <v>264.7345497805312</v>
       </c>
       <c r="G78" t="n">
-        <v>113.8795224070041</v>
+        <v>193.2886157398919</v>
       </c>
       <c r="H78" t="n">
-        <v>31.91135535166459</v>
+        <v>46.71173569148802</v>
       </c>
     </row>
     <row r="79">
@@ -3250,32 +3258,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[290.75, 236.78, 307.9]</t>
+          <t>[514.28, 893.84, 876.47]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>[352.82, 350.02, 466.45]</t>
+          <t>[400.39, 403.4, 435.75]</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>118.0605770830391</v>
+        <v>386.3241900416218</v>
       </c>
       <c r="G79" t="n">
-        <v>111.2869880553217</v>
+        <v>348.3503633192877</v>
       </c>
       <c r="H79" t="n">
-        <v>27.97863213645904</v>
+        <v>83.72073305752492</v>
       </c>
     </row>
     <row r="80">
@@ -3286,32 +3294,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[270.33, 350.89, 243.16]</t>
+          <t>[752.18, 739.26, 977.67]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>[350.02, 466.45, 494.05]</t>
+          <t>[403.4, 435.75, 517.7]</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>165.9810511203805</v>
+        <v>376.5375603229792</v>
       </c>
       <c r="G80" t="n">
-        <v>148.7124550948256</v>
+        <v>370.7551342619429</v>
       </c>
       <c r="H80" t="n">
-        <v>32.7745396105605</v>
+        <v>81.65414656130804</v>
       </c>
     </row>
     <row r="81">
@@ -3322,32 +3330,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[419.67, 290.24, 626.9]</t>
+          <t>[475.9, 633.11, 337.37]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[466.45, 494.05, 744.54]</t>
+          <t>[435.75, 517.7, 379.9]</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>138.5248046280923</v>
+        <v>74.69870345425726</v>
       </c>
       <c r="G81" t="n">
-        <v>122.7445910415628</v>
+        <v>66.02858650108642</v>
       </c>
       <c r="H81" t="n">
-        <v>22.36106482667982</v>
+        <v>14.23368684692681</v>
       </c>
     </row>
     <row r="82">
@@ -3358,32 +3366,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[2406.52, 2832.93, 3227.12]</t>
+          <t>[4613.96, 4864.93, 3831.63]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[2452.32, 3173.15, 4104.82]</t>
+          <t>[4488.08, 4264.39, 3418.05]</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>544.1203727276053</v>
+        <v>427.2165677276548</v>
       </c>
       <c r="G82" t="n">
-        <v>421.2400156583283</v>
+        <v>379.998390319903</v>
       </c>
       <c r="H82" t="n">
-        <v>11.32389170544695</v>
+        <v>9.662395703411557</v>
       </c>
     </row>
     <row r="83">
@@ -3394,32 +3402,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[2842.95, 3230.55, 2810.22]</t>
+          <t>[4829.91, 3807.47, 6761.18]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>[3173.15, 4104.82, 3231.51]</t>
+          <t>[4264.39, 3418.05, 5708.5]</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>591.8539416801361</v>
+        <v>725.6239546787675</v>
       </c>
       <c r="G83" t="n">
-        <v>541.9214804715352</v>
+        <v>669.2065883904141</v>
       </c>
       <c r="H83" t="n">
-        <v>14.91391024972791</v>
+        <v>14.36503716670651</v>
       </c>
     </row>
     <row r="84">
@@ -3430,32 +3438,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[3315.2, 2877.83, 2819.15]</t>
+          <t>[3707.44, 6567.55, 15132.27]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[4104.82, 3231.51, 3215.25]</t>
+          <t>[3418.05, 5708.5, 15350.76]</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>549.3884351133174</v>
+        <v>538.3474009737166</v>
       </c>
       <c r="G84" t="n">
-        <v>513.1331637786051</v>
+        <v>455.6426245719103</v>
       </c>
       <c r="H84" t="n">
-        <v>14.16684931292828</v>
+        <v>8.312788344257436</v>
       </c>
     </row>
     <row r="85">
@@ -3466,32 +3474,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[3008.22, 2948.87, 4952.78]</t>
+          <t>[6458.6, 14883.02, 2482.74]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[3231.51, 3215.25, 4352.03]</t>
+          <t>[5708.5, 15350.76, 2386.42]</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>400.7146485843116</v>
+        <v>513.3877084300518</v>
       </c>
       <c r="G85" t="n">
-        <v>363.4729331248538</v>
+        <v>438.0516711490598</v>
       </c>
       <c r="H85" t="n">
-        <v>9.666178403982862</v>
+        <v>6.741054652187424</v>
       </c>
     </row>
     <row r="86">
@@ -3502,32 +3510,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[2995.35, 5031.15, 2329.55]</t>
+          <t>[14571.48, 2422.6, 3050.52]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[3215.25, 4352.03, 2461.28]</t>
+          <t>[15350.76, 2386.42, 3163.3]</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>419.0908557575662</v>
+        <v>455.0863922466756</v>
       </c>
       <c r="G86" t="n">
-        <v>343.5815544474547</v>
+        <v>309.4135384874694</v>
       </c>
       <c r="H86" t="n">
-        <v>9.265285184134637</v>
+        <v>3.385916251592644</v>
       </c>
     </row>
     <row r="87">
@@ -3538,32 +3546,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[5111.85, 2367.15, 4719.07]</t>
+          <t>[2446.21, 3086.83, 3809.37]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[4352.03, 2461.28, 4488.08]</t>
+          <t>[2386.42, 3163.3, 2715.0]</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>461.7129564470075</v>
+        <v>634.3158642972842</v>
       </c>
       <c r="G87" t="n">
-        <v>361.6447519915061</v>
+        <v>410.2109103437754</v>
       </c>
       <c r="H87" t="n">
-        <v>8.810016866851338</v>
+        <v>15.07708168166913</v>
       </c>
     </row>
     <row r="88">
@@ -3574,32 +3582,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[2283.61, 4539.97, 4785.61]</t>
+          <t>[3071.65, 3791.1, 2998.58]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[2461.28, 4488.08, 4264.39]</t>
+          <t>[3163.3, 2715.0, 3245.04]</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>319.3399257770735</v>
+        <v>639.5673541756086</v>
       </c>
       <c r="G88" t="n">
-        <v>250.261661977045</v>
+        <v>471.4025748077908</v>
       </c>
       <c r="H88" t="n">
-        <v>6.865852101492388</v>
+        <v>16.70919154174503</v>
       </c>
     </row>
     <row r="89">
@@ -3610,32 +3618,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[4613.96, 4864.93, 3831.63]</t>
+          <t>[3815.82, 3017.6, 2960.47]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[4488.08, 4264.39, 3418.05]</t>
+          <t>[2715.0, 3245.04, 3464.3]</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>427.2165677276548</v>
+        <v>711.1891789915569</v>
       </c>
       <c r="G89" t="n">
-        <v>379.998390319903</v>
+        <v>610.6945277864201</v>
       </c>
       <c r="H89" t="n">
-        <v>9.662395703411557</v>
+        <v>20.69933067267577</v>
       </c>
     </row>
     <row r="90">
@@ -3646,32 +3654,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[4829.91, 3807.47, 6761.18]</t>
+          <t>[2785.09, 2729.56, 4057.74]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[4264.39, 3418.05, 5708.5]</t>
+          <t>[3245.04, 3464.3, 6448.97]</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>725.6239546787675</v>
+        <v>1468.489726087397</v>
       </c>
       <c r="G90" t="n">
-        <v>669.2065883904141</v>
+        <v>1195.308912650074</v>
       </c>
       <c r="H90" t="n">
-        <v>14.36503716670651</v>
+        <v>24.15409852844833</v>
       </c>
     </row>
     <row r="91">
@@ -3682,32 +3690,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[3707.44, 6567.55, 15132.27]</t>
+          <t>[2835.31, 4202.17, 2204.41]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>[3418.05, 5708.5, 15350.76]</t>
+          <t>[3464.3, 6448.97, 2419.61]</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>538.3474009737166</v>
+        <v>1352.78277357386</v>
       </c>
       <c r="G91" t="n">
-        <v>455.6426245719103</v>
+        <v>1030.332230117621</v>
       </c>
       <c r="H91" t="n">
-        <v>8.312788344257436</v>
+        <v>20.6300668039793</v>
       </c>
     </row>
     <row r="92">
@@ -3718,32 +3726,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[2684.99, 3352.0, 4309.05]</t>
+          <t>[3342.85, 5703.81, 3582.97]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>[2800.48, 3363.48, 4578.07]</t>
+          <t>[3873.69, 5466.61, 3586.35]</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>169.1541585798064</v>
+        <v>335.6901678149217</v>
       </c>
       <c r="G92" t="n">
-        <v>131.9947986722736</v>
+        <v>257.1408371997906</v>
       </c>
       <c r="H92" t="n">
-        <v>3.447119375531745</v>
+        <v>6.045704714794519</v>
       </c>
     </row>
     <row r="93">
@@ -3754,32 +3762,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[3373.57, 4336.59, 3573.09]</t>
+          <t>[5864.61, 3682.97, 4619.1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>[3363.48, 4578.07, 3984.34]</t>
+          <t>[5466.61, 3586.35, 4578.05]</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>275.4056135593559</v>
+        <v>237.6461923664545</v>
       </c>
       <c r="G93" t="n">
-        <v>220.9406781962151</v>
+        <v>178.5556173296241</v>
       </c>
       <c r="H93" t="n">
-        <v>5.298790971643056</v>
+        <v>3.623741643726556</v>
       </c>
     </row>
     <row r="94">
@@ -3790,32 +3798,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[4334.45, 3571.42, 4025.89]</t>
+          <t>[3629.79, 4552.43, 8830.89]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[4578.07, 3984.34, 4216.8]</t>
+          <t>[3586.35, 4578.05, 9000.38]</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>297.9348391321154</v>
+        <v>102.0942082623746</v>
       </c>
       <c r="G94" t="n">
-        <v>282.4800328344275</v>
+        <v>79.51490030287853</v>
       </c>
       <c r="H94" t="n">
-        <v>6.737388916055615</v>
+        <v>1.217971958372556</v>
       </c>
     </row>
     <row r="95">
@@ -3826,32 +3834,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[3600.27, 4058.08, 7888.64]</t>
+          <t>[4542.58, 8813.56, 2834.87]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>[3984.34, 4216.8, 7897.55]</t>
+          <t>[4578.05, 9000.38, 2582.26]</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>239.986759724923</v>
+        <v>182.5460876830903</v>
       </c>
       <c r="G95" t="n">
-        <v>183.9005507752634</v>
+        <v>158.2980012529086</v>
       </c>
       <c r="H95" t="n">
-        <v>4.50544152551503</v>
+        <v>4.21094294084856</v>
       </c>
     </row>
     <row r="96">
@@ -3862,32 +3870,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[4004.13, 8119.21, 2892.64]</t>
+          <t>[8824.85, 2838.51, 3528.42]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>[4216.8, 7897.55, 3133.14]</t>
+          <t>[9000.38, 2582.26, 3443.42]</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>225.2430819477462</v>
+        <v>185.9226010763803</v>
       </c>
       <c r="G96" t="n">
-        <v>224.9444187631188</v>
+        <v>172.2617379793392</v>
       </c>
       <c r="H96" t="n">
-        <v>5.175390543216177</v>
+        <v>4.780819067018242</v>
       </c>
     </row>
     <row r="97">
@@ -3898,32 +3906,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[8036.93, 2912.65, 3311.14]</t>
+          <t>[2847.6, 3539.65, 4574.29]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[7897.55, 3133.14, 3873.69]</t>
+          <t>[2582.26, 3443.42, 4863.53]</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>358.0048865156367</v>
+        <v>233.327361798715</v>
       </c>
       <c r="G97" t="n">
-        <v>307.4725657051572</v>
+        <v>216.9358301854146</v>
       </c>
       <c r="H97" t="n">
-        <v>7.774811032422899</v>
+        <v>6.339062465249973</v>
       </c>
     </row>
     <row r="98">
@@ -3934,32 +3942,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[2904.72, 3302.62, 5635.93]</t>
+          <t>[3484.65, 4503.56, 3730.06]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[3133.14, 3873.69, 5466.61]</t>
+          <t>[3443.42, 4863.53, 3999.99]</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>368.3139093187573</v>
+        <v>260.8567129239273</v>
       </c>
       <c r="G98" t="n">
-        <v>322.9363764749162</v>
+        <v>223.7101670654174</v>
       </c>
       <c r="H98" t="n">
-        <v>8.37667974038354</v>
+        <v>5.115688919789823</v>
       </c>
     </row>
     <row r="99">
@@ -3970,32 +3978,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[3342.85, 5703.81, 3582.97]</t>
+          <t>[4496.15, 3723.86, 4170.29]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>[3873.69, 5466.61, 3586.35]</t>
+          <t>[4863.53, 3999.99, 4231.86]</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>335.6901678149217</v>
+        <v>267.7098700666758</v>
       </c>
       <c r="G99" t="n">
-        <v>257.1408371997906</v>
+        <v>235.0258820729778</v>
       </c>
       <c r="H99" t="n">
-        <v>6.045704714794519</v>
+        <v>5.303971487102647</v>
       </c>
     </row>
     <row r="100">
@@ -4006,32 +4014,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[5864.61, 3682.97, 4619.1]</t>
+          <t>[3767.61, 4218.7, 8168.47]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>[5466.61, 3586.35, 4578.05]</t>
+          <t>[3999.99, 4231.86, 8235.66]</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>237.6461923664545</v>
+        <v>139.8677770449035</v>
       </c>
       <c r="G100" t="n">
-        <v>178.5556173296241</v>
+        <v>104.2445983119551</v>
       </c>
       <c r="H100" t="n">
-        <v>3.623741643726556</v>
+        <v>2.312125023922389</v>
       </c>
     </row>
     <row r="101">
@@ -4042,32 +4050,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[3629.79, 4552.43, 8830.89]</t>
+          <t>[4191.56, 8174.46, 3089.75]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>[3586.35, 4578.05, 9000.38]</t>
+          <t>[4231.86, 8235.66, 3753.95]</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>102.0942082623746</v>
+        <v>385.8037600086994</v>
       </c>
       <c r="G101" t="n">
-        <v>79.51490030287853</v>
+        <v>255.2342365855534</v>
       </c>
       <c r="H101" t="n">
-        <v>1.217971958372556</v>
+        <v>6.462961809699386</v>
       </c>
     </row>
     <row r="102">
@@ -4078,32 +4086,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[2450.99, 1889.2, 2695.45]</t>
+          <t>[2968.26, 5805.82, 2798.14]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>[2230.16, 1689.58, 2326.63]</t>
+          <t>[3097.3, 5874.2, 2631.65]</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>273.6413304437438</v>
+        <v>127.8619457802315</v>
       </c>
       <c r="G102" t="n">
-        <v>263.0874406953708</v>
+        <v>121.3041791960595</v>
       </c>
       <c r="H102" t="n">
-        <v>12.52282085003759</v>
+        <v>3.885578697742221</v>
       </c>
     </row>
     <row r="103">
@@ -4114,32 +4122,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[1809.77, 2611.54, 1590.41]</t>
+          <t>[5934.05, 2859.68, 4302.61]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>[1689.58, 2326.63, 1697.95]</t>
+          <t>[5874.2, 2631.65, 4280.1]</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>189.0181483511888</v>
+        <v>136.7282833860175</v>
       </c>
       <c r="G103" t="n">
-        <v>170.8797762348258</v>
+        <v>103.4603050931449</v>
       </c>
       <c r="H103" t="n">
-        <v>8.564236871313147</v>
+        <v>3.403141668298459</v>
       </c>
     </row>
     <row r="104">
@@ -4150,32 +4158,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[2514.01, 1530.93, 2240.49]</t>
+          <t>[2845.02, 4282.13, 7015.95]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[2326.63, 1697.95, 2179.57]</t>
+          <t>[2631.65, 4280.1, 6972.33]</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>149.1305891644025</v>
+        <v>125.7408093816002</v>
       </c>
       <c r="G104" t="n">
-        <v>138.441926418963</v>
+        <v>86.33878520790556</v>
       </c>
       <c r="H104" t="n">
-        <v>6.895198875606241</v>
+        <v>2.926920748171753</v>
       </c>
     </row>
     <row r="105">
@@ -4186,32 +4194,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[1463.0, 2151.93, 6128.64]</t>
+          <t>[4115.66, 6752.17, 2240.37]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>[1697.95, 2179.57, 6701.44]</t>
+          <t>[4280.1, 6972.33, 2251.02]</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>357.8025594366188</v>
+        <v>158.7713286764572</v>
       </c>
       <c r="G105" t="n">
-        <v>278.4636942016448</v>
+        <v>131.7509445567106</v>
       </c>
       <c r="H105" t="n">
-        <v>7.884299520631149</v>
+        <v>2.490932191891607</v>
       </c>
     </row>
     <row r="106">
@@ -4222,32 +4230,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[2317.1, 6617.29, 2021.84]</t>
+          <t>[6877.76, 2276.71, 1783.27]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>[2179.57, 6701.44, 2190.31]</t>
+          <t>[6972.33, 2251.02, 1655.31]</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>134.6324795374077</v>
+        <v>93.05414693995192</v>
       </c>
       <c r="G106" t="n">
-        <v>130.0495819930206</v>
+        <v>82.73947074529686</v>
       </c>
       <c r="H106" t="n">
-        <v>5.085771756694083</v>
+        <v>3.409262629991557</v>
       </c>
     </row>
     <row r="107">
@@ -4258,32 +4266,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[6420.35, 1963.11, 2780.56]</t>
+          <t>[2293.38, 1795.96, 2583.29]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[6701.44, 2190.31, 3097.3]</t>
+          <t>[2251.02, 1655.31, 2404.24]</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>277.4618754317072</v>
+        <v>133.709465992393</v>
       </c>
       <c r="G107" t="n">
-        <v>275.0099494214713</v>
+        <v>120.6855993515408</v>
       </c>
       <c r="H107" t="n">
-        <v>8.264615028911782</v>
+        <v>5.941929068240611</v>
       </c>
     </row>
     <row r="108">
@@ -4294,32 +4302,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[2006.61, 2841.46, 5564.84]</t>
+          <t>[1778.3, 2558.92, 1744.81]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>[2190.31, 3097.3, 5874.2]</t>
+          <t>[1655.31, 2404.24, 1792.75]</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>254.8885622610825</v>
+        <v>117.4044113757558</v>
       </c>
       <c r="G108" t="n">
-        <v>249.6344743135103</v>
+        <v>108.5369754894623</v>
       </c>
       <c r="H108" t="n">
-        <v>7.304545316808055</v>
+        <v>5.512610568240127</v>
       </c>
     </row>
     <row r="109">
@@ -4330,32 +4338,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[2968.26, 5805.82, 2798.14]</t>
+          <t>[2469.2, 1687.91, 2235.42]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>[3097.3, 5874.2, 2631.65]</t>
+          <t>[2404.24, 1792.75, 2202.71]</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>127.8619457802315</v>
+        <v>73.66883405810344</v>
       </c>
       <c r="G109" t="n">
-        <v>121.3041791960595</v>
+        <v>67.50324629367499</v>
       </c>
       <c r="H109" t="n">
-        <v>3.885578697742221</v>
+        <v>3.34495964840524</v>
       </c>
     </row>
     <row r="110">
@@ -4366,32 +4374,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[5934.05, 2859.68, 4302.61]</t>
+          <t>[1665.73, 2206.81, 6640.56]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>[5874.2, 2631.65, 4280.1]</t>
+          <t>[1792.75, 2202.71, 6945.26]</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>136.7282833860175</v>
+        <v>190.6057996431866</v>
       </c>
       <c r="G110" t="n">
-        <v>103.4603050931449</v>
+        <v>145.2729659401365</v>
       </c>
       <c r="H110" t="n">
-        <v>3.403141668298459</v>
+        <v>3.886198589212275</v>
       </c>
     </row>
     <row r="111">
@@ -4402,32 +4410,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[2845.02, 4282.13, 7015.95]</t>
+          <t>[2284.47, 6890.63, 2163.29]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>[2631.65, 4280.1, 6972.33]</t>
+          <t>[2202.71, 6945.26, 2125.57]</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>125.7408093816002</v>
+        <v>60.80628248878998</v>
       </c>
       <c r="G111" t="n">
-        <v>86.33878520790556</v>
+        <v>58.03841066740688</v>
       </c>
       <c r="H111" t="n">
-        <v>2.926920748171753</v>
+        <v>2.091035040429175</v>
       </c>
     </row>
     <row r="112">
@@ -4438,32 +4446,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[2956.32, 4103.87, 3162.09]</t>
+          <t>[3197.89, 4616.85, 1776.45]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>[2833.58, 4113.6, 3293.47]</t>
+          <t>[2421.12, 3723.42, 1925.96]</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>103.9535323818547</v>
+        <v>688.9488154417854</v>
       </c>
       <c r="G112" t="n">
-        <v>87.94725535261159</v>
+        <v>606.5731359242324</v>
       </c>
       <c r="H112" t="n">
-        <v>2.852335320331307</v>
+        <v>21.28042123489795</v>
       </c>
     </row>
     <row r="113">
@@ -4474,32 +4482,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[4045.47, 3117.38, 3247.49]</t>
+          <t>[4190.35, 1613.65, 1717.46]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>[4113.6, 3293.47, 3185.67]</t>
+          <t>[3723.42, 1925.96, 1575.93]</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>114.7034958495356</v>
+        <v>334.4628498103204</v>
       </c>
       <c r="G113" t="n">
-        <v>102.0144218509082</v>
+        <v>306.9252621471799</v>
       </c>
       <c r="H113" t="n">
-        <v>2.981168818608713</v>
+        <v>12.5790354834074</v>
       </c>
     </row>
     <row r="114">
@@ -4510,32 +4518,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[3134.75, 3265.56, 4668.71]</t>
+          <t>[1556.36, 1657.01, 2696.96]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>[3293.47, 3185.67, 4139.04]</t>
+          <t>[1925.96, 1575.93, 2429.17]</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>322.5533845980983</v>
+        <v>267.6383530571027</v>
       </c>
       <c r="G114" t="n">
-        <v>256.0918965724051</v>
+        <v>239.4912783461934</v>
       </c>
       <c r="H114" t="n">
-        <v>6.707945054872654</v>
+        <v>11.78648715147378</v>
       </c>
     </row>
     <row r="115">
@@ -4546,32 +4554,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[3320.42, 4746.21, 5276.76]</t>
+          <t>[1767.45, 2874.97, 3354.47]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>[3185.67, 4139.04, 8752.92]</t>
+          <t>[1575.93, 2429.17, 2922.22]</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2038.830925834242</v>
+        <v>375.1719633442349</v>
       </c>
       <c r="G115" t="n">
-        <v>1406.026189300599</v>
+        <v>356.5242816420538</v>
       </c>
       <c r="H115" t="n">
-        <v>19.53782323760235</v>
+        <v>15.0988739563013</v>
       </c>
     </row>
     <row r="116">
@@ -4582,32 +4590,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[4680.88, 5204.55, 1362.69]</t>
+          <t>[2776.19, 3241.0, 4516.28]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>[4139.04, 8752.92, 1902.17]</t>
+          <t>[2429.17, 2922.22, 3988.12]</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2095.672445204433</v>
+        <v>408.6553742238553</v>
       </c>
       <c r="G116" t="n">
-        <v>1543.227954076248</v>
+        <v>397.987690690464</v>
       </c>
       <c r="H116" t="n">
-        <v>27.33048767167118</v>
+        <v>12.81261119535822</v>
       </c>
     </row>
     <row r="117">
@@ -4618,32 +4626,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[4994.16, 1308.07, 2487.4]</t>
+          <t>[3114.97, 4341.4, 3356.45]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>[8752.92, 1902.17, 2421.12]</t>
+          <t>[2922.22, 3988.12, 3137.83]</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2197.393849595682</v>
+        <v>264.4199455378701</v>
       </c>
       <c r="G117" t="n">
-        <v>1473.047427445919</v>
+        <v>254.8835708195753</v>
       </c>
       <c r="H117" t="n">
-        <v>25.63777865706837</v>
+        <v>7.473865939530204</v>
       </c>
     </row>
     <row r="118">
@@ -4654,32 +4662,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[1565.58, 2971.18, 4292.25]</t>
+          <t>[4257.96, 3292.3, 3402.77]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>[1902.17, 2421.12, 3723.42]</t>
+          <t>[3988.12, 3137.83, 3184.39]</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>496.4652775220172</v>
+        <v>219.3635853192233</v>
       </c>
       <c r="G118" t="n">
-        <v>485.1615131865319</v>
+        <v>214.2271420916015</v>
       </c>
       <c r="H118" t="n">
-        <v>18.5638168267773</v>
+        <v>6.182162457684159</v>
       </c>
     </row>
     <row r="119">
@@ -4690,32 +4698,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[3197.89, 4616.85, 1776.45]</t>
+          <t>[3227.26, 3335.92, 4723.03]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>[2421.12, 3723.42, 1925.96]</t>
+          <t>[3137.83, 3184.39, 4128.53]</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>688.9488154417854</v>
+        <v>357.9519660630964</v>
       </c>
       <c r="G119" t="n">
-        <v>606.5731359242324</v>
+        <v>278.4856683408186</v>
       </c>
       <c r="H119" t="n">
-        <v>21.28042123489795</v>
+        <v>7.336094975068992</v>
       </c>
     </row>
     <row r="120">
@@ -4726,32 +4734,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[4190.35, 1613.65, 1717.46]</t>
+          <t>[3307.6, 4683.09, 5552.27]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>[3723.42, 1925.96, 1575.93]</t>
+          <t>[3184.39, 4128.53, 4248.12]</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>334.4628498103204</v>
+        <v>821.2851341501275</v>
       </c>
       <c r="G120" t="n">
-        <v>306.9252621471799</v>
+        <v>660.6409668406233</v>
       </c>
       <c r="H120" t="n">
-        <v>12.5790354834074</v>
+        <v>16.00037626384186</v>
       </c>
     </row>
     <row r="121">
@@ -4762,32 +4770,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[1556.36, 1657.01, 2696.96]</t>
+          <t>[4628.81, 5488.36, 1410.46]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[1925.96, 1575.93, 2429.17]</t>
+          <t>[4128.53, 4248.12, 1555.87]</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>267.6383530571027</v>
+        <v>776.6615135325355</v>
       </c>
       <c r="G121" t="n">
-        <v>239.4912783461934</v>
+        <v>628.6427466688907</v>
       </c>
       <c r="H121" t="n">
-        <v>11.78648715147378</v>
+        <v>16.8862007636187</v>
       </c>
     </row>
     <row r="122">
@@ -4798,32 +4806,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[1333.02, 1112.66, 1232.1]</t>
+          <t>[1558.92, 1677.72, 1849.93]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>[1389.65, 1031.91, 1089.57]</t>
+          <t>[1581.37, 1724.95, 1919.48]</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>100.0718500212842</v>
+        <v>50.23877375628959</v>
       </c>
       <c r="G122" t="n">
-        <v>93.30430546937805</v>
+        <v>46.41127381749251</v>
       </c>
       <c r="H122" t="n">
-        <v>8.327303203454932</v>
+        <v>2.593785174295704</v>
       </c>
     </row>
     <row r="123">
@@ -4834,32 +4842,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[1143.58, 1265.41, 1605.72]</t>
+          <t>[1686.82, 1859.87, 1826.54]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>[1031.91, 1089.57, 1336.93]</t>
+          <t>[1724.95, 1919.48, 1838.46]</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>196.3323246634384</v>
+        <v>41.42950829619432</v>
       </c>
       <c r="G123" t="n">
-        <v>185.4335655777355</v>
+        <v>36.55301225975487</v>
       </c>
       <c r="H123" t="n">
-        <v>15.68839122619621</v>
+        <v>1.9881173144618</v>
       </c>
     </row>
     <row r="124">
@@ -4870,32 +4878,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[1204.32, 1532.48, 1407.34]</t>
+          <t>[1874.9, 1841.37, 2860.49]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>[1089.57, 1336.93, 1269.08]</t>
+          <t>[1919.48, 1838.46, 2285.11]</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>153.321886714597</v>
+        <v>333.1977567316803</v>
       </c>
       <c r="G124" t="n">
-        <v>149.5193602675409</v>
+        <v>207.624435296122</v>
       </c>
       <c r="H124" t="n">
-        <v>12.01761101845973</v>
+        <v>9.220152252241347</v>
       </c>
     </row>
     <row r="125">
@@ -4906,32 +4914,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[1476.78, 1358.18, 1625.37]</t>
+          <t>[1856.74, 2885.67, 1227.89]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>[1336.93, 1269.08, 1472.82]</t>
+          <t>[1838.46, 2285.11, 1341.74]</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>130.0859270760483</v>
+        <v>353.0672764995625</v>
       </c>
       <c r="G125" t="n">
-        <v>127.1655152358274</v>
+        <v>244.2301253041782</v>
       </c>
       <c r="H125" t="n">
-        <v>9.279608216784096</v>
+        <v>11.92034259232967</v>
       </c>
     </row>
     <row r="126">
@@ -4942,32 +4950,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[1313.35, 1572.02, 1386.53]</t>
+          <t>[2875.4, 1223.55, 932.93]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[1269.08, 1472.82, 1271.54]</t>
+          <t>[2285.11, 1341.74, 1075.34]</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>91.33107368150282</v>
+        <v>357.1593822933551</v>
       </c>
       <c r="G126" t="n">
-        <v>86.15564826295856</v>
+        <v>283.629421828591</v>
       </c>
       <c r="H126" t="n">
-        <v>6.422544311896207</v>
+        <v>15.96130911440298</v>
       </c>
     </row>
     <row r="127">
@@ -4978,32 +4986,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[1552.94, 1369.54, 1623.7]</t>
+          <t>[1163.73, 908.94, 992.52]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>[1472.82, 1271.54, 1581.37]</t>
+          <t>[1341.74, 1075.34, 1109.61]</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>77.06100895865512</v>
+        <v>156.0846581184672</v>
       </c>
       <c r="G127" t="n">
-        <v>73.48292723374091</v>
+        <v>153.8344788197122</v>
       </c>
       <c r="H127" t="n">
-        <v>5.274607236631208</v>
+        <v>13.0979792204056</v>
       </c>
     </row>
     <row r="128">
@@ -5014,32 +5022,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[1343.01, 1591.74, 1713.06]</t>
+          <t>[970.95, 1048.17, 1317.88]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>[1271.54, 1581.37, 1724.95]</t>
+          <t>[1075.34, 1109.61, 1429.88]</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>42.25452185999335</v>
+        <v>95.24511796946987</v>
       </c>
       <c r="G128" t="n">
-        <v>31.24303303649435</v>
+        <v>92.60845180589888</v>
       </c>
       <c r="H128" t="n">
-        <v>2.321886184959741</v>
+        <v>7.692387741440617</v>
       </c>
     </row>
     <row r="129">
@@ -5050,32 +5058,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[1558.92, 1677.72, 1849.93]</t>
+          <t>[1083.4, 1360.06, 1277.71]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>[1581.37, 1724.95, 1919.48]</t>
+          <t>[1109.61, 1429.88, 1463.98]</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>50.23877375628959</v>
+        <v>115.8432369341821</v>
       </c>
       <c r="G129" t="n">
-        <v>46.41127381749251</v>
+        <v>94.10140718468544</v>
       </c>
       <c r="H129" t="n">
-        <v>2.593785174295704</v>
+        <v>6.656299606304644</v>
       </c>
     </row>
     <row r="130">
@@ -5086,32 +5094,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[1686.82, 1859.87, 1826.54]</t>
+          <t>[1371.0, 1287.77, 1523.24]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>[1724.95, 1919.48, 1838.46]</t>
+          <t>[1429.88, 1463.98, 1578.15]</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>41.42950829619432</v>
+        <v>111.8534157800555</v>
       </c>
       <c r="G130" t="n">
-        <v>36.55301225975487</v>
+        <v>96.66921441054417</v>
       </c>
       <c r="H130" t="n">
-        <v>1.9881173144618</v>
+        <v>6.544705632478869</v>
       </c>
     </row>
     <row r="131">
@@ -5122,32 +5130,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[1874.9, 1841.37, 2860.49]</t>
+          <t>[1306.39, 1545.11, 1366.68]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[1919.48, 1838.46, 2285.11]</t>
+          <t>[1463.98, 1578.15, 1481.05]</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>333.1977567316803</v>
+        <v>114.0281145977893</v>
       </c>
       <c r="G131" t="n">
-        <v>207.624435296122</v>
+        <v>101.6672299187967</v>
       </c>
       <c r="H131" t="n">
-        <v>9.220152252241347</v>
+        <v>6.860139741839681</v>
       </c>
     </row>
     <row r="132">
@@ -5158,32 +5166,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[82.58, 113.47, 86.77]</t>
+          <t>[109.66, 206.87, 215.14]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>[95.22, 128.9, 95.28]</t>
+          <t>[84.38, 242.24, 168.08]</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>12.51828552303713</v>
+        <v>36.99241482420591</v>
       </c>
       <c r="G132" t="n">
-        <v>12.19152501002769</v>
+        <v>35.90567737316794</v>
       </c>
       <c r="H132" t="n">
-        <v>11.39046245184547</v>
+        <v>24.18774506461941</v>
       </c>
     </row>
     <row r="133">
@@ -5194,32 +5202,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[117.19, 89.62, 263.0]</t>
+          <t>[193.28, 201.18, 276.15]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>[128.9, 95.28, 274.28]</t>
+          <t>[242.24, 168.08, 258.08]</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>9.942211745875705</v>
+        <v>35.68206809531958</v>
       </c>
       <c r="G133" t="n">
-        <v>9.552688835540158</v>
+        <v>33.37772668844743</v>
       </c>
       <c r="H133" t="n">
-        <v>6.381302552306846</v>
+        <v>15.63591788193784</v>
       </c>
     </row>
     <row r="134">
@@ -5230,32 +5238,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[91.61, 268.8, 50.85]</t>
+          <t>[213.33, 292.65, 771.45]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>[95.28, 274.28, 199.88]</t>
+          <t>[168.08, 258.08, 517.28]</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>86.12564141272945</v>
+        <v>150.3811561272621</v>
       </c>
       <c r="G134" t="n">
-        <v>52.72757292052112</v>
+        <v>111.3283565423777</v>
       </c>
       <c r="H134" t="n">
-        <v>26.80411641274518</v>
+        <v>29.81692649694542</v>
       </c>
     </row>
     <row r="135">
@@ -5266,32 +5274,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[271.24, 51.32, 233.61]</t>
+          <t>[275.15, 725.87, 105.99]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>[274.28, 199.88, 221.98]</t>
+          <t>[258.08, 517.28, 99.24]</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>86.05027947037064</v>
+        <v>120.8974793241819</v>
       </c>
       <c r="G135" t="n">
-        <v>54.41083565385755</v>
+        <v>77.46943717413363</v>
       </c>
       <c r="H135" t="n">
-        <v>26.89104772397329</v>
+        <v>17.91221121238782</v>
       </c>
     </row>
     <row r="136">
@@ -5302,32 +5310,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[51.46, 234.22, 111.49]</t>
+          <t>[713.94, 104.24, 160.44]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>[199.88, 221.98, 100.98]</t>
+          <t>[517.28, 99.24, 132.08]</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>86.19694092554779</v>
+        <v>114.7526649780693</v>
       </c>
       <c r="G136" t="n">
-        <v>57.05885843552983</v>
+        <v>76.67605394652165</v>
       </c>
       <c r="H136" t="n">
-        <v>30.06050851835014</v>
+        <v>21.51190740225694</v>
       </c>
     </row>
     <row r="137">
@@ -5338,32 +5346,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[226.34, 134.03, 118.78]</t>
+          <t>[95.83, 147.63, 112.25]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>[221.98, 100.98, 84.38]</t>
+          <t>[99.24, 132.08, 103.05]</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>27.65353941910604</v>
+        <v>10.61851578855921</v>
       </c>
       <c r="G137" t="n">
-        <v>23.93378682560622</v>
+        <v>9.38986960349745</v>
       </c>
       <c r="H137" t="n">
-        <v>25.15089714321215</v>
+        <v>8.04848407233472</v>
       </c>
     </row>
     <row r="138">
@@ -5374,32 +5382,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[133.29, 118.13, 222.63]</t>
+          <t>[149.0, 113.3, 227.1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>[100.98, 84.38, 242.24]</t>
+          <t>[132.08, 103.05, 279.48]</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>29.2549279916527</v>
+        <v>32.3302675824301</v>
       </c>
       <c r="G138" t="n">
-        <v>28.55618839402175</v>
+        <v>26.52083474089728</v>
       </c>
       <c r="H138" t="n">
-        <v>26.69687108299556</v>
+        <v>13.83571648878739</v>
       </c>
     </row>
     <row r="139">
@@ -5410,32 +5418,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[109.66, 206.87, 215.14]</t>
+          <t>[109.74, 220.04, 80.57]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>[84.38, 242.24, 168.08]</t>
+          <t>[103.05, 279.48, 40.3]</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>36.99241482420591</v>
+        <v>41.62999651297422</v>
       </c>
       <c r="G139" t="n">
-        <v>35.90567737316794</v>
+        <v>35.46641295563098</v>
       </c>
       <c r="H139" t="n">
-        <v>24.18774506461941</v>
+        <v>42.56201343169327</v>
       </c>
     </row>
     <row r="140">
@@ -5446,32 +5454,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[193.28, 201.18, 276.15]</t>
+          <t>[216.46, 79.22, 171.88]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>[242.24, 168.08, 258.08]</t>
+          <t>[279.48, 40.3, 226.0]</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>35.68206809531958</v>
+        <v>52.96105055069091</v>
       </c>
       <c r="G140" t="n">
-        <v>33.37772668844743</v>
+        <v>52.01862885527482</v>
       </c>
       <c r="H140" t="n">
-        <v>15.63591788193784</v>
+        <v>47.69281037785469</v>
       </c>
     </row>
     <row r="141">
@@ -5482,32 +5490,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[213.33, 292.65, 771.45]</t>
+          <t>[84.73, 183.66, 106.04]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>[168.08, 258.08, 517.28]</t>
+          <t>[40.3, 226.0, 98.66]</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>150.3811561272621</v>
+        <v>35.6909635638712</v>
       </c>
       <c r="G141" t="n">
-        <v>111.3283565423777</v>
+        <v>31.38476931927546</v>
       </c>
       <c r="H141" t="n">
-        <v>29.81692649694542</v>
+        <v>45.48883440343459</v>
       </c>
     </row>
     <row r="142">
@@ -5518,32 +5526,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[5713.53, 3623.67, 3320.67]</t>
+          <t>[3254.88, 5454.81, 3833.46]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>[5644.09, 3549.25, 3114.29]</t>
+          <t>[3114.29, 5453.19, 3460.45]</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>132.857211059088</v>
+        <v>230.148656348345</v>
       </c>
       <c r="G142" t="n">
-        <v>116.74667284136</v>
+        <v>171.7426604292071</v>
       </c>
       <c r="H142" t="n">
-        <v>3.318002950044738</v>
+        <v>5.107831122681581</v>
       </c>
     </row>
     <row r="143">
@@ -5554,32 +5562,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[3581.46, 3283.65, 5501.63]</t>
+          <t>[5225.99, 3677.34, 6299.28]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>[3549.25, 3114.29, 5453.19]</t>
+          <t>[5453.19, 3460.45, 5847.3]</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>103.3868143177493</v>
+        <v>317.7767753535308</v>
       </c>
       <c r="G143" t="n">
-        <v>83.33497696578115</v>
+        <v>298.6903311863496</v>
       </c>
       <c r="H143" t="n">
-        <v>2.411287485509603</v>
+        <v>6.054598904934588</v>
       </c>
     </row>
     <row r="144">
@@ -5590,32 +5598,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[3254.88, 5454.81, 3833.46]</t>
+          <t>[3832.2, 6556.14, 16679.6]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>[3114.29, 5453.19, 3460.45]</t>
+          <t>[3460.45, 5847.3, 18068.25]</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>230.148656348345</v>
+        <v>925.3838413117082</v>
       </c>
       <c r="G144" t="n">
-        <v>171.7426604292071</v>
+        <v>823.0805136466712</v>
       </c>
       <c r="H144" t="n">
-        <v>5.107831122681581</v>
+        <v>10.18364630957557</v>
       </c>
     </row>
     <row r="145">
@@ -5626,32 +5634,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[5225.99, 3677.34, 6299.28]</t>
+          <t>[5939.0, 15158.24, 1403.44]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>[5453.19, 3460.45, 5847.3]</t>
+          <t>[5847.3, 18068.25, 1999.86]</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>317.7767753535308</v>
+        <v>1715.835420481276</v>
       </c>
       <c r="G145" t="n">
-        <v>298.6903311863496</v>
+        <v>1199.373928730761</v>
       </c>
       <c r="H145" t="n">
-        <v>6.054598904934588</v>
+        <v>15.83224849691022</v>
       </c>
     </row>
     <row r="146">
@@ -5662,1472 +5670,2012 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[3832.2, 6556.14, 16679.6]</t>
+          <t>[14931.69, 1383.11, 1921.76]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>[3460.45, 5847.3, 18068.25]</t>
+          <t>[18068.25, 1999.86, 2813.21]</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>925.3838413117082</v>
+        <v>1915.990659631532</v>
       </c>
       <c r="G146" t="n">
-        <v>823.0805136466712</v>
+        <v>1548.250433098305</v>
       </c>
       <c r="H146" t="n">
-        <v>10.18364630957557</v>
+        <v>26.62892973852347</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[10342.47, 945.45, 2754.86]</t>
+          <t>[1663.21, 2296.21, 2731.07]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>[8860.62, 1923.47, 2568.13]</t>
+          <t>[1999.86, 2813.21, 3152.38]</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1030.73944077299</v>
+        <v>431.3259527295021</v>
       </c>
       <c r="G147" t="n">
-        <v>882.1997829255665</v>
+        <v>424.9877594672896</v>
       </c>
       <c r="H147" t="n">
-        <v>24.9472341492401</v>
+        <v>16.1920772555396</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[815.26, 2390.81, 7061.71]</t>
+          <t>[2743.82, 3242.22, 2756.63]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>[1923.47, 2568.13, 7223.75]</t>
+          <t>[2813.21, 3152.38, 2634.39]</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>654.6811623535928</v>
+        <v>96.3123484824108</v>
       </c>
       <c r="G148" t="n">
-        <v>482.5231843418374</v>
+        <v>93.82215343195276</v>
       </c>
       <c r="H148" t="n">
-        <v>22.25429181580162</v>
+        <v>3.318840734369097</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[3628.8, 10529.61, 9830.79]</t>
+          <t>[3321.86, 2821.68, 3206.6]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[2568.13, 7223.75, 6626.0]</t>
+          <t>[3152.38, 2634.39, 2757.33]</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2727.906420413332</v>
+        <v>297.5719688129407</v>
       </c>
       <c r="G149" t="n">
-        <v>2523.774390580963</v>
+        <v>268.6805279225748</v>
       </c>
       <c r="H149" t="n">
-        <v>45.14400524668507</v>
+        <v>9.593136941410437</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[8789.13, 8250.18, 9472.22]</t>
+          <t>[2682.89, 3054.79, 6790.59]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>[7223.75, 6626.0, 6669.33]</t>
+          <t>[2634.39, 2757.33, 6965.91]</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2077.226823915973</v>
+        <v>201.3075767134328</v>
       </c>
       <c r="G150" t="n">
-        <v>1997.487102745741</v>
+        <v>173.7622558637466</v>
       </c>
       <c r="H150" t="n">
-        <v>29.40295337532121</v>
+        <v>5.048709957445376</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[7796.62, 8968.9, 13045.98]</t>
+          <t>[3001.67, 6677.42, 4204.87]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[6626.0, 6669.33, 12413.16]</t>
+          <t>[2757.33, 6965.91, 2293.91]</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1533.931561011418</v>
+        <v>1124.679126054698</v>
       </c>
       <c r="G151" t="n">
-        <v>1367.671081832399</v>
+        <v>814.5980795184172</v>
       </c>
       <c r="H151" t="n">
-        <v>19.08161717994723</v>
+        <v>32.10293585719198</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[904.9, 102.96, 529.16]</t>
+          <t>[3628.8, 10529.61, 9830.79]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[847.75, 99.5, 593.1]</t>
+          <t>[2568.13, 7223.75, 6626.0]</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>49.55385172641216</v>
+        <v>2727.906420413332</v>
       </c>
       <c r="G152" t="n">
-        <v>41.518934523953</v>
+        <v>2523.774390580963</v>
       </c>
       <c r="H152" t="n">
-        <v>7.001231169930625</v>
+        <v>45.14400524668507</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[98.47, 507.22, 866.26]</t>
+          <t>[8789.13, 8250.18, 9472.22]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[99.5, 593.1, 750.95]</t>
+          <t>[7223.75, 6626.0, 6669.33]</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>83.01426172191434</v>
+        <v>2077.226823915973</v>
       </c>
       <c r="G153" t="n">
-        <v>67.40873164535061</v>
+        <v>1997.487102745741</v>
       </c>
       <c r="H153" t="n">
-        <v>10.29043549490256</v>
+        <v>29.40295337532121</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[510.6, 871.88, 526.4]</t>
+          <t>[7796.62, 8968.9, 13045.98]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[593.1, 750.95, 507.0]</t>
+          <t>[6626.0, 6669.33, 12413.16]</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>85.25732262847967</v>
+        <v>1533.931561011418</v>
       </c>
       <c r="G154" t="n">
-        <v>74.27768169382944</v>
+        <v>1367.671081832399</v>
       </c>
       <c r="H154" t="n">
-        <v>11.28023814448049</v>
+        <v>19.08161717994723</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[958.19, 576.68, 466.88]</t>
+          <t>[8623.63, 12560.1, 2353.57]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[750.95, 507.0, 248.25]</t>
+          <t>[6669.33, 12413.16, 2489.12]</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>178.5179708938655</v>
+        <v>1134.201018214441</v>
       </c>
       <c r="G155" t="n">
-        <v>165.1848548931449</v>
+        <v>745.595931894026</v>
       </c>
       <c r="H155" t="n">
-        <v>43.13686231398173</v>
+        <v>11.97738857800488</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[496.16, 403.46, 1422.61]</t>
+          <t>[11743.24, 2206.09, 1550.71]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[507.0, 248.25, 1142.3]</t>
+          <t>[12413.16, 2489.12, 1770.35]</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>185.0970982040299</v>
+        <v>438.6105826433349</v>
       </c>
       <c r="G156" t="n">
-        <v>148.7859148236635</v>
+        <v>390.8637688139349</v>
       </c>
       <c r="H156" t="n">
-        <v>29.73248037948108</v>
+        <v>9.72477771534847</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[2891.33, 3433.59, 3921.4]</t>
+          <t>[2243.42, 1575.75, 7191.07]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[2459.35, 2801.67, 2741.18]</t>
+          <t>[2489.12, 1770.35, 7699.85]</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>812.1695717986935</v>
+        <v>345.0082680080871</v>
       </c>
       <c r="G157" t="n">
-        <v>748.0418822529469</v>
+        <v>316.358808442505</v>
       </c>
       <c r="H157" t="n">
-        <v>27.72510291386434</v>
+        <v>9.156889708987874</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[3255.26, 3719.74, 3012.27]</t>
+          <t>[1616.36, 7368.81, 1996.06]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[2801.67, 2741.18, 2948.03]</t>
+          <t>[1770.35, 7699.85, 2296.43]</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>623.8202685295028</v>
+        <v>272.9618464105365</v>
       </c>
       <c r="G158" t="n">
-        <v>498.7982031456625</v>
+        <v>261.801614461615</v>
       </c>
       <c r="H158" t="n">
-        <v>18.0225757731832</v>
+        <v>8.692575561960169</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[3574.97, 2896.17, 3185.76]</t>
+          <t>[7523.99, 2036.46, 2638.37]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[2741.18, 2948.03, 3140.46]</t>
+          <t>[7699.85, 2296.43, 2733.24]</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>483.0254773251374</v>
+        <v>189.3057082197558</v>
       </c>
       <c r="G159" t="n">
-        <v>310.3147471899124</v>
+        <v>176.8988259550478</v>
       </c>
       <c r="H159" t="n">
-        <v>11.20619751408607</v>
+        <v>5.691820308602798</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[2680.37, 2950.48, 3595.36]</t>
+          <t>[2047.67, 2652.13, 9810.52]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[2948.03, 3140.46, 4609.38]</t>
+          <t>[2296.43, 2733.24, 9527.94]</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>615.3537062676116</v>
+        <v>222.3434207298211</v>
       </c>
       <c r="G160" t="n">
-        <v>490.5562866208635</v>
+        <v>204.1481582497395</v>
       </c>
       <c r="H160" t="n">
-        <v>12.37600806221856</v>
+        <v>5.588580286161045</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[3046.8, 3711.83, 3784.32]</t>
+          <t>[2727.05, 10064.91, 1224.55]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[3140.46, 4609.38, 5306.59]</t>
+          <t>[2733.24, 9527.94, 1344.41]</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1021.710703869692</v>
+        <v>317.6696907805587</v>
       </c>
       <c r="G161" t="n">
-        <v>837.8264316447088</v>
+        <v>221.0055770948082</v>
       </c>
       <c r="H161" t="n">
-        <v>17.04699253543036</v>
+        <v>4.925798205216933</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[3741.27, 3814.29, 2932.69]</t>
+          <t>[510.6, 871.88, 526.4]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[4609.38, 5306.59, 4061.35]</t>
+          <t>[593.1, 750.95, 507.0]</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1190.864756015212</v>
+        <v>85.25732262847967</v>
       </c>
       <c r="G162" t="n">
-        <v>1163.027483297812</v>
+        <v>74.27768169382944</v>
       </c>
       <c r="H162" t="n">
-        <v>24.91524065451865</v>
+        <v>11.28023814448049</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[4005.99, 3078.69, 3767.84]</t>
+          <t>[958.19, 576.68, 466.88]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[5306.59, 4061.35, 4014.27]</t>
+          <t>[750.95, 507.0, 248.25]</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>951.8263797631442</v>
+        <v>178.5179708938655</v>
       </c>
       <c r="G163" t="n">
-        <v>843.2312274339984</v>
+        <v>165.1848548931449</v>
       </c>
       <c r="H163" t="n">
-        <v>18.28116096210955</v>
+        <v>43.13686231398173</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[3345.4, 4091.78, 4910.62]</t>
+          <t>[496.16, 403.46, 1422.61]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[4061.35, 4014.27, 4697.04]</t>
+          <t>[507.0, 248.25, 1142.3]</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>433.6671029133699</v>
+        <v>185.0970982040299</v>
       </c>
       <c r="G164" t="n">
-        <v>335.6774467315997</v>
+        <v>148.7859148236635</v>
       </c>
       <c r="H164" t="n">
-        <v>8.035389094643856</v>
+        <v>29.73248037948108</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[4517.88, 5419.11, 7606.44]</t>
+          <t>[408.86, 1440.92, 975.85]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[4014.27, 4697.04, 5946.29]</t>
+          <t>[248.25, 1142.3, 1319.15]</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1084.912359538261</v>
+        <v>278.5832081149971</v>
       </c>
       <c r="G165" t="n">
-        <v>961.9433994908267</v>
+        <v>267.5113307188406</v>
       </c>
       <c r="H165" t="n">
-        <v>18.61249240408007</v>
+        <v>38.95482888349861</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[5130.97, 7205.12, 8867.02]</t>
+          <t>[1060.68, 725.64, 271.32]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>[4697.04, 5946.29, 7538.52]</t>
+          <t>[1142.3, 1319.15, 464.08]</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1085.948335914159</v>
+        <v>363.3531090903996</v>
       </c>
       <c r="G166" t="n">
-        <v>1007.086416788542</v>
+        <v>289.2966592523256</v>
       </c>
       <c r="H166" t="n">
-        <v>16.01040343163427</v>
+        <v>31.22427789110754</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[3970.5, 2188.64, 1507.98]</t>
+          <t>[760.45, 283.92, 331.93]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[3942.12, 2622.99, 1708.04]</t>
+          <t>[1319.15, 464.08, 401.05]</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>276.5790639998209</v>
+        <v>341.2617595591584</v>
       </c>
       <c r="G167" t="n">
-        <v>220.9301058711535</v>
+        <v>269.3266731141607</v>
       </c>
       <c r="H167" t="n">
-        <v>9.664040801521489</v>
+        <v>32.80301820236358</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[2183.81, 1504.79, 1795.1]</t>
+          <t>[390.05, 450.86, 199.63]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[2622.99, 1708.04, 1714.33]</t>
+          <t>[464.08, 401.05, 179.6]</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>283.263897341307</v>
+        <v>52.79871376511986</v>
       </c>
       <c r="G168" t="n">
-        <v>241.0655709907526</v>
+        <v>47.95811811877826</v>
       </c>
       <c r="H168" t="n">
-        <v>11.11809180151092</v>
+        <v>13.1753025886052</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[1589.27, 1896.03, 2144.63]</t>
+          <t>[504.81, 222.79, 474.98]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[1708.04, 1714.33, 1907.73]</t>
+          <t>[401.05, 179.6, 443.45]</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>185.5094235900521</v>
+        <v>67.39149693305666</v>
       </c>
       <c r="G169" t="n">
-        <v>179.1222442940831</v>
+        <v>59.49124050792778</v>
       </c>
       <c r="H169" t="n">
-        <v>9.990070925548729</v>
+        <v>19.00967370833982</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[1941.0, 2194.51, 1413.95]</t>
+          <t>[194.1, 415.89, 869.75]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>[1714.33, 1907.73, 1447.97]</t>
+          <t>[179.6, 443.45, 854.7]</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>211.9574366794605</v>
+        <v>19.968057301581</v>
       </c>
       <c r="G170" t="n">
-        <v>182.4886759975429</v>
+        <v>19.03588798931326</v>
       </c>
       <c r="H170" t="n">
-        <v>10.20128868152955</v>
+        <v>5.348935925525923</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[2113.91, 1363.33, 2644.17]</t>
+          <t>[397.79, 833.55, 95.95]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>[1907.73, 1447.97, 2345.72]</t>
+          <t>[443.45, 854.7, 103.1]</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>215.0564048852547</v>
+        <v>29.34553398779571</v>
       </c>
       <c r="G171" t="n">
-        <v>196.4241472651983</v>
+        <v>24.6528759941582</v>
       </c>
       <c r="H171" t="n">
-        <v>9.792109079265153</v>
+        <v>6.568299418271091</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[1325.36, 2570.91, 3805.75]</t>
+          <t>[3345.4, 4091.78, 4910.62]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[1447.97, 2345.72, 3472.15]</t>
+          <t>[4061.35, 4014.27, 4697.04]</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>242.9219727740456</v>
+        <v>433.6671029133699</v>
       </c>
       <c r="G172" t="n">
-        <v>227.1340534722673</v>
+        <v>335.6774467315997</v>
       </c>
       <c r="H172" t="n">
-        <v>9.225265158999569</v>
+        <v>8.035389094643856</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[2632.52, 3897.95, 5909.1]</t>
+          <t>[4517.88, 5419.11, 7606.44]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>[2345.72, 3472.15, 5090.14]</t>
+          <t>[4014.27, 4697.04, 5946.29]</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>558.0477192102298</v>
+        <v>1084.912359538261</v>
       </c>
       <c r="G173" t="n">
-        <v>510.5197782685589</v>
+        <v>961.9433994908267</v>
       </c>
       <c r="H173" t="n">
-        <v>13.52634027841189</v>
+        <v>18.61249240408007</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[3779.6, 5731.71, 2411.09]</t>
+          <t>[5130.97, 7205.12, 8867.02]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>[3472.15, 5090.14, 2367.75]</t>
+          <t>[4697.04, 5946.29, 7538.52]</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>411.5075875661966</v>
+        <v>1085.948335914159</v>
       </c>
       <c r="G174" t="n">
-        <v>330.7869632232972</v>
+        <v>1007.086416788542</v>
       </c>
       <c r="H174" t="n">
-        <v>7.763130010445535</v>
+        <v>16.01040343163427</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[5600.47, 2354.83, 2150.6]</t>
+          <t>[6992.93, 8607.92, 2901.79]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>[5090.14, 2367.75, 2041.65]</t>
+          <t>[5946.29, 7538.52, 2478.9]</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>301.3705197800415</v>
+        <v>897.7604836600115</v>
       </c>
       <c r="G175" t="n">
-        <v>210.7338130307132</v>
+        <v>846.312023280189</v>
       </c>
       <c r="H175" t="n">
-        <v>5.302667170547172</v>
+        <v>16.28234098746861</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[2291.44, 2092.18, 3865.25]</t>
+          <t>[8215.22, 2771.43, 3278.41]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[2367.75, 2041.65, 3772.16]</t>
+          <t>[7538.52, 2478.9, 2439.47]</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>75.36876751424735</v>
+        <v>644.8062005450594</v>
       </c>
       <c r="G176" t="n">
-        <v>73.30764432830604</v>
+        <v>602.7259432962211</v>
       </c>
       <c r="H176" t="n">
-        <v>2.721780127215857</v>
+        <v>18.38930181812132</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[5499.3, 5808.21, 6642.13]</t>
+          <t>[2699.92, 3194.84, 3594.56]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[6351.97, 11020.91, 7050.97]</t>
+          <t>[2478.9, 2439.47, 2864.2]</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>3058.670673252589</v>
+        <v>619.9097516044797</v>
       </c>
       <c r="G177" t="n">
-        <v>2158.068681006594</v>
+        <v>568.9169258493633</v>
       </c>
       <c r="H177" t="n">
-        <v>22.17343130308268</v>
+        <v>21.79339562793582</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[6032.33, 6881.17, 7969.83]</t>
+          <t>[3097.84, 3486.41, 2905.6]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>[11020.91, 7050.97, 9224.01]</t>
+          <t>[2439.47, 2864.2, 2872.67]</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2971.40405807367</v>
+        <v>523.3517220459415</v>
       </c>
       <c r="G178" t="n">
-        <v>2137.518656180265</v>
+        <v>437.8394859583568</v>
       </c>
       <c r="H178" t="n">
-        <v>20.42323732592304</v>
+        <v>16.61952338038981</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[8447.86, 7905.26, 7828.37]</t>
+          <t>[3133.66, 2613.54, 2868.22]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[7050.97, 9224.01, 6776.16]</t>
+          <t>[2864.2, 2872.67, 2706.78]</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1264.587604122288</v>
+        <v>235.1042723065561</v>
       </c>
       <c r="G179" t="n">
-        <v>1255.949559706518</v>
+        <v>230.011792852831</v>
       </c>
       <c r="H179" t="n">
-        <v>16.54544518221052</v>
+        <v>8.13095611184848</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[7704.37, 7633.0, 7800.06]</t>
+          <t>[2495.03, 2739.4, 3403.41]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[9224.01, 6776.16, 15715.54]</t>
+          <t>[2872.67, 2706.78, 4220.25]</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>4679.683940009854</v>
+        <v>519.9080780077858</v>
       </c>
       <c r="G180" t="n">
-        <v>3430.653873883814</v>
+        <v>409.035798126885</v>
       </c>
       <c r="H180" t="n">
-        <v>26.4956562199814</v>
+        <v>11.23551315163994</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[7828.78, 7997.0, 7430.95]</t>
+          <t>[2919.27, 3624.7, 3742.33]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[6776.16, 15715.54, 6948.86]</t>
+          <t>[2706.78, 4220.25, 4780.77]</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>4506.151940544874</v>
+        <v>701.9466086558728</v>
       </c>
       <c r="G181" t="n">
-        <v>3084.415812441827</v>
+        <v>615.4916282434725</v>
       </c>
       <c r="H181" t="n">
-        <v>23.86197048259963</v>
+        <v>14.56100582206051</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[7842.97, 7289.94, 8800.3]</t>
+          <t>[3779.6, 5731.71, 2411.09]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[15715.54, 6948.86, 9372.79]</t>
+          <t>[3472.15, 5090.14, 2367.75]</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>4561.484632638584</v>
+        <v>411.5075875661966</v>
       </c>
       <c r="G182" t="n">
-        <v>2928.713188650116</v>
+        <v>330.7869632232972</v>
       </c>
       <c r="H182" t="n">
-        <v>20.37020128380463</v>
+        <v>7.763130010445535</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[7926.49, 9556.52, 10605.77]</t>
+          <t>[5600.47, 2354.83, 2150.6]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>[6948.86, 9372.79, 15738.07]</t>
+          <t>[5090.14, 2367.75, 2041.65]</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3018.278853449384</v>
+        <v>301.3705197800415</v>
       </c>
       <c r="G183" t="n">
-        <v>2097.886801292635</v>
+        <v>210.7338130307132</v>
       </c>
       <c r="H183" t="n">
-        <v>16.21330090595886</v>
+        <v>5.302667170547172</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[9381.81, 10415.31, 11429.82]</t>
+          <t>[2291.44, 2092.18, 3865.25]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[9372.79, 15738.07, 10566.5]</t>
+          <t>[2367.75, 2041.65, 3772.16]</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3113.262834534491</v>
+        <v>75.36876751424735</v>
       </c>
       <c r="G184" t="n">
-        <v>2065.033536544025</v>
+        <v>73.30764432830604</v>
       </c>
       <c r="H184" t="n">
-        <v>14.02916591457095</v>
+        <v>2.721780127215857</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[10415.3, 11429.26, 11406.99]</t>
+          <t>[2112.3, 3903.34, 3802.28]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>[15738.07, 10566.5, 11441.98]</t>
+          <t>[2041.65, 3772.16, 4007.77]</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3113.275566480481</v>
+        <v>146.543105174791</v>
       </c>
       <c r="G185" t="n">
-        <v>2073.507419163286</v>
+        <v>135.7715208424089</v>
       </c>
       <c r="H185" t="n">
-        <v>14.09728577317255</v>
+        <v>4.021703606974516</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[3865.41, 3765.96, 2323.64]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[3772.16, 4007.77, 2335.19]</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>149.7771870788131</v>
+      </c>
+      <c r="G186" t="n">
+        <v>115.5365346927536</v>
+      </c>
+      <c r="H186" t="n">
+        <v>3.000084461914607</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[3740.82, 2307.72, 1495.72]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[4007.77, 2335.19, 2064.27]</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>362.9812995047298</v>
+      </c>
+      <c r="G187" t="n">
+        <v>287.6575096211549</v>
+      </c>
+      <c r="H187" t="n">
+        <v>11.79323729183421</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[2351.2, 1525.09, 1628.53]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[2335.19, 2064.27, 1625.97]</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>311.4339171933176</v>
+      </c>
+      <c r="G188" t="n">
+        <v>185.9167189818344</v>
+      </c>
+      <c r="H188" t="n">
+        <v>8.987586586444131</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[1522.3, 1625.62, 1852.56]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[2064.27, 1625.97, 1849.39]</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>312.9091055188396</v>
+      </c>
+      <c r="G189" t="n">
+        <v>181.829534330058</v>
+      </c>
+      <c r="H189" t="n">
+        <v>8.815905326251066</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[1768.69, 2012.68, 1443.22]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[1625.97, 1849.39, 1416.17]</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>126.1776639453942</v>
+      </c>
+      <c r="G190" t="n">
+        <v>111.0175402873655</v>
+      </c>
+      <c r="H190" t="n">
+        <v>6.505525242428216</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[1961.0, 1409.78, 2432.98]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[1849.39, 1416.17, 2324.16]</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>90.0752114016697</v>
+      </c>
+      <c r="G191" t="n">
+        <v>75.60756728549138</v>
+      </c>
+      <c r="H191" t="n">
+        <v>3.722790542339754</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[9381.81, 10415.31, 11429.82]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[9372.79, 15738.07, 10566.5]</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>3113.262834534491</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2065.033536544025</v>
+      </c>
+      <c r="H192" t="n">
+        <v>14.02916591457095</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[10415.3, 11429.26, 11406.99]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[15738.07, 10566.5, 11441.98]</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>3113.275566480481</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2073.507419163286</v>
+      </c>
+      <c r="H193" t="n">
+        <v>14.09728577317255</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>[12079.92, 12043.47, 16473.56]</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>[10566.5, 11441.98, 29353.24]</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F194" t="n">
         <v>7495.296126502002</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G194" t="n">
         <v>4998.196895738903</v>
       </c>
-      <c r="H186" t="n">
+      <c r="H194" t="n">
         <v>21.15263735000804</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[11747.27, 16076.7, 7751.41]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[11441.98, 29353.24, 8467.16]</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>7678.365641546461</v>
+      </c>
+      <c r="G195" t="n">
+        <v>4765.859109762394</v>
+      </c>
+      <c r="H195" t="n">
+        <v>18.78387909741622</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[16022.43, 7725.59, 8414.84]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[29353.24, 8467.16, 8032.34]</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>7711.607055610837</v>
+      </c>
+      <c r="G196" t="n">
+        <v>4818.291345727269</v>
+      </c>
+      <c r="H196" t="n">
+        <v>19.64508784117455</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>[8502.0, 9247.63, 9596.6]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[8467.16, 8032.34, 8225.02]</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>1058.203454810857</v>
+      </c>
+      <c r="G197" t="n">
+        <v>873.9045627371992</v>
+      </c>
+      <c r="H197" t="n">
+        <v>10.73906093096468</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[9238.26, 9587.77, 9462.39]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[8032.34, 8225.02, 6628.3]</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>1944.511972245985</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1800.918886091537</v>
+      </c>
+      <c r="H198" t="n">
+        <v>24.7796760648979</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[9325.64, 9208.63, 8660.17]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[8225.02, 6628.3, 7697.58]</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>1712.312864012599</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1547.847664525018</v>
+      </c>
+      <c r="H199" t="n">
+        <v>21.60516048564021</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[8541.04, 8046.88, 9217.04]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[6628.3, 7697.58, 9167.36]</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>1122.950712654138</v>
+      </c>
+      <c r="G200" t="n">
+        <v>770.5746484735837</v>
+      </c>
+      <c r="H200" t="n">
+        <v>11.31231057809351</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[8184.3, 9441.33, 7882.08]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[7697.58, 9167.36, 8580.29]</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>516.2210078152096</v>
+      </c>
+      <c r="G201" t="n">
+        <v>486.3008893483481</v>
+      </c>
+      <c r="H201" t="n">
+        <v>5.816322402894309</v>
       </c>
     </row>
   </sheetData>
